--- a/outputs/marine_equipment/Перечень_для_отгрузки.xlsx
+++ b/outputs/marine_equipment/Перечень_для_отгрузки.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>286 позиций  2 902 шт  27.30 т. Порядок как грузим: сверху самая крупная арматура  дальше по убыванию диаметра.</t>
+          <t>286 позиций  2 902 шт  27.30 т. Порядок как грузим: сверху самая крупная арматура  дальше по убыванию диаметра  в самом конце вентиляционные головки.</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2579,7 @@
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Головки вентиляционные — 7 позиций  43 шт  363 кг</t>
+          <t>Фланцевая угловая — 27 позиций  100 шт  1 748 кг</t>
         </is>
       </c>
       <c r="B76" s="4" t="n"/>
@@ -2598,26 +2598,26 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>Грибки АМГ Ду 200 с нижнем приводом</t>
+          <t>Клапан фланцевый угловой Ду150 Ру10</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="D77" s="5" t="inlineStr"/>
-      <c r="E77" s="12" t="inlineStr">
-        <is>
-          <t>(541-03.316-04)</t>
-        </is>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr"/>
       <c r="F77" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>4.7</v>
+        <v>68.7</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="I77" s="11" t="n"/>
       <c r="J77" s="11" t="n"/>
@@ -2628,26 +2628,30 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Грибки АМГ Ду 150 (верхние)</t>
+          <t>Клапан фланцевый угловой Ду150 Ру10</t>
         </is>
       </c>
       <c r="C78" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="D78" s="5" t="inlineStr"/>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>(541-03.315-02)</t>
+          <t>521-01.207</t>
         </is>
       </c>
       <c r="F78" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>2.9</v>
+        <v>68.7</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="I78" s="11" t="n"/>
       <c r="J78" s="11" t="n"/>
@@ -2658,26 +2662,22 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Грибки АМГ Ду 150 (нижние)</t>
+          <t>Клапан фланцевый угловой Ду100</t>
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D79" s="5" t="inlineStr"/>
-      <c r="E79" s="12" t="inlineStr">
-        <is>
-          <t>(541-03.316-02)</t>
-        </is>
-      </c>
+      <c r="E79" s="7" t="inlineStr"/>
       <c r="F79" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>2.7</v>
+        <v>28</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>5</v>
+        <v>280</v>
       </c>
       <c r="I79" s="11" t="n"/>
       <c r="J79" s="11" t="n"/>
@@ -2688,26 +2688,26 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду125 (без поплавка)</t>
+          <t>Клапан фланцевый угловой Ду80</t>
         </is>
       </c>
       <c r="C80" s="5" t="n">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="D80" s="5" t="inlineStr"/>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>(541-03.220)</t>
+          <t>522-03.197</t>
         </is>
       </c>
       <c r="F80" s="8" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>18.2</v>
+        <v>25</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>109</v>
+        <v>700</v>
       </c>
       <c r="I80" s="11" t="n"/>
       <c r="J80" s="11" t="n"/>
@@ -2718,26 +2718,28 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду80</t>
+          <t>Клапан фланцевый угловой Ду65 Ру10</t>
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="D81" s="5" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>(541-03.218)</t>
+          <t>522-35.4154-02</t>
         </is>
       </c>
       <c r="F81" s="8" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>11.2</v>
+        <v>16</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>213</v>
+        <v>48</v>
       </c>
       <c r="I81" s="11" t="n"/>
       <c r="J81" s="11" t="n"/>
@@ -2748,26 +2750,30 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду32</t>
+          <t>Клапан фланцевый угловой Ду65 Ру10</t>
         </is>
       </c>
       <c r="C82" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="D82" s="5" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>541-03.224</t>
+          <t>522-35.4154-02</t>
         </is>
       </c>
       <c r="F82" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>1.5</v>
+        <v>17</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="I82" s="11" t="n"/>
       <c r="J82" s="11" t="n"/>
@@ -2778,453 +2784,473 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду25</t>
+          <t>Клапан фланцевый угловой Ду65 Ру10</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="D83" s="5" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>(541-03.232)</t>
+          <t>522-35.4201</t>
         </is>
       </c>
       <c r="F83" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>1.6</v>
+        <v>17</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="I83" s="11" t="n"/>
       <c r="J83" s="11" t="n"/>
     </row>
-    <row r="84" ht="22" customHeight="1">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>Фланцевая угловая — 27 позиций  100 шт  1 748 кг</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="n"/>
-      <c r="C84" s="4" t="n"/>
-      <c r="D84" s="4" t="n"/>
-      <c r="E84" s="4" t="n"/>
-      <c r="F84" s="4" t="n"/>
-      <c r="G84" s="4" t="n"/>
-      <c r="H84" s="4" t="n"/>
-      <c r="I84" s="4" t="n"/>
-      <c r="J84" s="4" t="n"/>
+    <row r="84" ht="26" customHeight="1">
+      <c r="A84" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый угловой Ду65 Ру10</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="inlineStr">
+        <is>
+          <t>521-03.195</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G84" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="H84" s="10" t="n">
+        <v>136</v>
+      </c>
+      <c r="I84" s="11" t="n"/>
+      <c r="J84" s="11" t="n"/>
     </row>
     <row r="85" ht="26" customHeight="1">
       <c r="A85" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду150 Ру10</t>
+          <t>Клапан фланцевый угловой Ду65 Ру40</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="D85" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E85" s="7" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
+        <is>
+          <t>521-03.230</t>
+        </is>
+      </c>
       <c r="F85" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>68.7</v>
+        <v>20</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="I85" s="11" t="n"/>
       <c r="J85" s="11" t="n"/>
     </row>
     <row r="86" ht="26" customHeight="1">
       <c r="A86" s="5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду150 Ру10</t>
+          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
         </is>
       </c>
       <c r="C86" s="5" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
-          <t>521-01.207</t>
+          <t>595-03.011</t>
         </is>
       </c>
       <c r="F86" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>68.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="I86" s="11" t="n"/>
       <c r="J86" s="11" t="n"/>
     </row>
     <row r="87" ht="26" customHeight="1">
       <c r="A87" s="5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду100</t>
+          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="D87" s="5" t="inlineStr"/>
-      <c r="E87" s="7" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
+        <is>
+          <t>595-03.008</t>
+        </is>
+      </c>
       <c r="F87" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>28</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>280</v>
+        <v>9</v>
       </c>
       <c r="I87" s="11" t="n"/>
       <c r="J87" s="11" t="n"/>
     </row>
     <row r="88" ht="26" customHeight="1">
       <c r="A88" s="5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду80</t>
+          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
         </is>
       </c>
       <c r="C88" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="D88" s="5" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="E88" s="12" t="inlineStr">
         <is>
-          <t>522-03.197</t>
+          <t>без чертежа</t>
         </is>
       </c>
       <c r="F88" s="8" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>25</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>700</v>
+        <v>19</v>
       </c>
       <c r="I88" s="11" t="n"/>
       <c r="J88" s="11" t="n"/>
     </row>
     <row r="89" ht="26" customHeight="1">
       <c r="A89" s="5" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду65 Ру10</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду50</t>
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="D89" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E89" s="12" t="inlineStr">
-        <is>
-          <t>522-35.4154-02</t>
-        </is>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D89" s="5" t="inlineStr"/>
+      <c r="E89" s="7" t="inlineStr"/>
       <c r="F89" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>16</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="I89" s="11" t="n"/>
       <c r="J89" s="11" t="n"/>
     </row>
     <row r="90" ht="26" customHeight="1">
       <c r="A90" s="5" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду65 Ру10</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
         </is>
       </c>
       <c r="C90" s="5" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>522-35.4154-02</t>
+          <t>595-3М-48</t>
         </is>
       </c>
       <c r="F90" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>17</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="I90" s="11" t="n"/>
       <c r="J90" s="11" t="n"/>
     </row>
     <row r="91" ht="26" customHeight="1">
       <c r="A91" s="5" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду65 Ру10</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>522-35.4201</t>
+          <t>595-35-021</t>
         </is>
       </c>
       <c r="F91" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>17</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="I91" s="11" t="n"/>
       <c r="J91" s="11" t="n"/>
     </row>
     <row r="92" ht="26" customHeight="1">
       <c r="A92" s="5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду65 Ру10</t>
+          <t>Клапан фланцевый угловой Ду50</t>
         </is>
       </c>
       <c r="C92" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E92" s="12" t="inlineStr">
-        <is>
-          <t>521-03.195</t>
-        </is>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D92" s="5" t="inlineStr"/>
+      <c r="E92" s="7" t="inlineStr"/>
       <c r="F92" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="I92" s="11" t="n"/>
       <c r="J92" s="11" t="n"/>
     </row>
     <row r="93" ht="26" customHeight="1">
       <c r="A93" s="5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду65 Ру40</t>
+          <t>Клапан угловой фланцевый Ду 40 - БРАК</t>
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="D93" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="E93" s="12" t="inlineStr">
-        <is>
-          <t>521-03.230</t>
-        </is>
-      </c>
+      <c r="D93" s="5" t="inlineStr"/>
+      <c r="E93" s="7" t="inlineStr"/>
       <c r="F93" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>20</v>
+        <v>5.6</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I93" s="11" t="n"/>
       <c r="J93" s="11" t="n"/>
     </row>
     <row r="94" ht="26" customHeight="1">
       <c r="A94" s="5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
+          <t>Клапан фланцевый угловой Ду40 Ру10</t>
         </is>
       </c>
       <c r="C94" s="5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E94" s="12" t="inlineStr">
         <is>
-          <t>595-03.011</t>
+          <t>522-03.202</t>
         </is>
       </c>
       <c r="F94" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>9.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="I94" s="11" t="n"/>
       <c r="J94" s="11" t="n"/>
     </row>
     <row r="95" ht="26" customHeight="1">
       <c r="A95" s="5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
+          <t>Клапан фланцевый угловой Ду40 Ру25</t>
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>595-03.008</t>
+          <t>521-01.200</t>
         </is>
       </c>
       <c r="F95" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>9.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="H95" s="10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I95" s="11" t="n"/>
       <c r="J95" s="11" t="n"/>
     </row>
     <row r="96" ht="26" customHeight="1">
       <c r="A96" s="5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
+          <t>Клапан фланцевый угловой Ду40 Ру25 сталь ок.входа</t>
         </is>
       </c>
       <c r="C96" s="5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E96" s="12" t="inlineStr">
         <is>
-          <t>без чертежа</t>
+          <t>522-35.445-19</t>
         </is>
       </c>
       <c r="F96" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G96" s="9" t="n">
-        <v>9.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="H96" s="10" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I96" s="11" t="n"/>
       <c r="J96" s="11" t="n"/>
     </row>
     <row r="97" ht="26" customHeight="1">
       <c r="A97" s="5" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду50</t>
+          <t>Клапан предохранит. фланцевый угловой Ду32Ру4 (524-03.090)</t>
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="D97" s="5" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="E97" s="7" t="inlineStr"/>
       <c r="F97" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="H97" s="10" t="n">
         <v>9</v>
@@ -3234,151 +3260,155 @@
     </row>
     <row r="98" ht="26" customHeight="1">
       <c r="A98" s="5" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру10</t>
         </is>
       </c>
       <c r="C98" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="D98" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+        <v>32</v>
+      </c>
+      <c r="D98" s="5" t="n">
+        <v>10</v>
       </c>
       <c r="E98" s="12" t="inlineStr">
         <is>
-          <t>595-3М-48</t>
+          <t>595-03-006</t>
         </is>
       </c>
       <c r="F98" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G98" s="9" t="n">
-        <v>9.300000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="H98" s="10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I98" s="11" t="n"/>
       <c r="J98" s="11" t="n"/>
     </row>
     <row r="99" ht="26" customHeight="1">
       <c r="A99" s="5" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру10</t>
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>595-35-021</t>
+          <t>595-03-006</t>
         </is>
       </c>
       <c r="F99" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>9.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="H99" s="10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I99" s="11" t="n"/>
       <c r="J99" s="11" t="n"/>
     </row>
     <row r="100" ht="26" customHeight="1">
       <c r="A100" s="5" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду50</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру16</t>
         </is>
       </c>
       <c r="C100" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="D100" s="5" t="inlineStr"/>
-      <c r="E100" s="7" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="D100" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E100" s="12" t="inlineStr">
+        <is>
+          <t>595-01-010</t>
+        </is>
+      </c>
       <c r="F100" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G100" s="9" t="n">
-        <v>12</v>
+        <v>5.4</v>
       </c>
       <c r="H100" s="10" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="I100" s="11" t="n"/>
       <c r="J100" s="11" t="n"/>
     </row>
     <row r="101" ht="26" customHeight="1">
       <c r="A101" s="5" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Клапан угловой фланцевый Ду 40 - БРАК</t>
+          <t>Клапан фланцевый угловой Ду25</t>
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D101" s="5" t="inlineStr"/>
-      <c r="E101" s="7" t="inlineStr"/>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>521-3М539</t>
+        </is>
+      </c>
       <c r="F101" s="8" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H101" s="10" t="n">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="I101" s="11" t="n"/>
       <c r="J101" s="11" t="n"/>
     </row>
     <row r="102" ht="26" customHeight="1">
       <c r="A102" s="5" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду40 Ру10</t>
+          <t>Клапан фланцевый угловой Ду25</t>
         </is>
       </c>
       <c r="C102" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="D102" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="D102" s="5" t="inlineStr"/>
       <c r="E102" s="12" t="inlineStr">
         <is>
-          <t>522-03.202</t>
+          <t>521-3М.123</t>
         </is>
       </c>
       <c r="F102" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G102" s="9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H102" s="10" t="n">
         <v>6</v>
@@ -3388,31 +3418,27 @@
     </row>
     <row r="103" ht="26" customHeight="1">
       <c r="A103" s="5" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду40 Ру25</t>
+          <t>Клапан фланцевый угловой Ду25</t>
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="D103" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="D103" s="5" t="inlineStr"/>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>521-01.200</t>
+          <t>521-3М539</t>
         </is>
       </c>
       <c r="F103" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H103" s="10" t="n">
         <v>6</v>
@@ -3420,39 +3446,21 @@
       <c r="I103" s="11" t="n"/>
       <c r="J103" s="11" t="n"/>
     </row>
-    <row r="104" ht="26" customHeight="1">
-      <c r="A104" s="5" t="n">
-        <v>94</v>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>Клапан фланцевый угловой Ду40 Ру25 сталь ок.входа</t>
-        </is>
-      </c>
-      <c r="C104" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="D104" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E104" s="12" t="inlineStr">
-        <is>
-          <t>522-35.445-19</t>
-        </is>
-      </c>
-      <c r="F104" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G104" s="9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H104" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="I104" s="11" t="n"/>
-      <c r="J104" s="11" t="n"/>
+    <row r="104" ht="22" customHeight="1">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>Без описания — уточнить — 6 позиций  8 шт  170 кг</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="n"/>
+      <c r="C104" s="4" t="n"/>
+      <c r="D104" s="4" t="n"/>
+      <c r="E104" s="4" t="n"/>
+      <c r="F104" s="4" t="n"/>
+      <c r="G104" s="4" t="n"/>
+      <c r="H104" s="4" t="n"/>
+      <c r="I104" s="4" t="n"/>
+      <c r="J104" s="4" t="n"/>
     </row>
     <row r="105" ht="26" customHeight="1">
       <c r="A105" s="5" t="n">
@@ -3460,26 +3468,22 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Клапан предохранит. фланцевый угловой Ду32Ру4 (524-03.090)</t>
+          <t>Клапан проходной ДУ 125 корпус</t>
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="D105" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="D105" s="5" t="inlineStr"/>
       <c r="E105" s="7" t="inlineStr"/>
       <c r="F105" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>9.5</v>
+        <v>135.3</v>
       </c>
       <c r="H105" s="10" t="n">
-        <v>9</v>
+        <v>135</v>
       </c>
       <c r="I105" s="11" t="n"/>
       <c r="J105" s="11" t="n"/>
@@ -3490,28 +3494,26 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру10</t>
+          <t>Клапан Ду20/10</t>
         </is>
       </c>
       <c r="C106" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="D106" s="5" t="n">
-        <v>10</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="D106" s="5" t="inlineStr"/>
       <c r="E106" s="12" t="inlineStr">
         <is>
-          <t>595-03-006</t>
+          <t>581-С6.73</t>
         </is>
       </c>
       <c r="F106" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G106" s="9" t="n">
-        <v>5.8</v>
+        <v>2.4</v>
       </c>
       <c r="H106" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I106" s="11" t="n"/>
       <c r="J106" s="11" t="n"/>
@@ -3522,30 +3524,26 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру10</t>
-        </is>
-      </c>
-      <c r="C107" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="D107" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>Кланан Рр18-2 45/25</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr"/>
+      <c r="D107" s="5" t="n">
+        <v>18</v>
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>595-03-006</t>
+          <t>2619802505</t>
         </is>
       </c>
       <c r="F107" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="H107" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I107" s="11" t="n"/>
       <c r="J107" s="11" t="n"/>
@@ -3556,28 +3554,24 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру16</t>
-        </is>
-      </c>
-      <c r="C108" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="D108" s="5" t="n">
-        <v>16</v>
-      </c>
+          <t>Кланан Рр18-2 45/25</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr"/>
+      <c r="D108" s="5" t="inlineStr"/>
       <c r="E108" s="12" t="inlineStr">
         <is>
-          <t>595-01-010</t>
+          <t>2619802505</t>
         </is>
       </c>
       <c r="F108" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G108" s="9" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="H108" s="10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I108" s="11" t="n"/>
       <c r="J108" s="11" t="n"/>
@@ -3588,26 +3582,24 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду25</t>
-        </is>
-      </c>
-      <c r="C109" s="5" t="n">
-        <v>25</v>
-      </c>
+          <t>Клапан</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr"/>
       <c r="D109" s="5" t="inlineStr"/>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>521-3М539</t>
+          <t>587-182.126</t>
         </is>
       </c>
       <c r="F109" s="8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="H109" s="10" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="I109" s="11" t="n"/>
       <c r="J109" s="11" t="n"/>
@@ -3618,75 +3610,65 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду25</t>
-        </is>
-      </c>
-      <c r="C110" s="5" t="n">
-        <v>25</v>
-      </c>
+          <t>Судовая запорная арматура</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr"/>
       <c r="D110" s="5" t="inlineStr"/>
-      <c r="E110" s="12" t="inlineStr">
-        <is>
-          <t>521-3М.123</t>
-        </is>
-      </c>
+      <c r="E110" s="7" t="inlineStr"/>
       <c r="F110" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G110" s="9" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="H110" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I110" s="11" t="n"/>
       <c r="J110" s="11" t="n"/>
     </row>
-    <row r="111" ht="26" customHeight="1">
-      <c r="A111" s="5" t="n">
+    <row r="111" ht="22" customHeight="1">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>Коробки клапанные — 11 позиций  65 шт  3 490 кг</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="n"/>
+      <c r="C111" s="4" t="n"/>
+      <c r="D111" s="4" t="n"/>
+      <c r="E111" s="4" t="n"/>
+      <c r="F111" s="4" t="n"/>
+      <c r="G111" s="4" t="n"/>
+      <c r="H111" s="4" t="n"/>
+      <c r="I111" s="4" t="n"/>
+      <c r="J111" s="4" t="n"/>
+    </row>
+    <row r="112" ht="26" customHeight="1">
+      <c r="A112" s="5" t="n">
         <v>101</v>
       </c>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>Клапан фланцевый угловой Ду25</t>
-        </is>
-      </c>
-      <c r="C111" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="D111" s="5" t="inlineStr"/>
-      <c r="E111" s="12" t="inlineStr">
-        <is>
-          <t>521-3М539</t>
-        </is>
-      </c>
-      <c r="F111" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G111" s="9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H111" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="I111" s="11" t="n"/>
-      <c r="J111" s="11" t="n"/>
-    </row>
-    <row r="112" ht="22" customHeight="1">
-      <c r="A112" s="4" t="inlineStr">
-        <is>
-          <t>Без описания — уточнить — 6 позиций  8 шт  170 кг</t>
-        </is>
-      </c>
-      <c r="B112" s="4" t="n"/>
-      <c r="C112" s="4" t="n"/>
-      <c r="D112" s="4" t="n"/>
-      <c r="E112" s="4" t="n"/>
-      <c r="F112" s="4" t="n"/>
-      <c r="G112" s="4" t="n"/>
-      <c r="H112" s="4" t="n"/>
-      <c r="I112" s="4" t="n"/>
-      <c r="J112" s="4" t="n"/>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>Коробка 3-х клап.фланцевая Ду100</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D112" s="5" t="inlineStr"/>
+      <c r="E112" s="7" t="inlineStr"/>
+      <c r="F112" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="9" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="H112" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="I112" s="11" t="n"/>
+      <c r="J112" s="11" t="n"/>
     </row>
     <row r="113" ht="26" customHeight="1">
       <c r="A113" s="5" t="n">
@@ -3694,22 +3676,22 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>Клапан проходной ДУ 125 корпус</t>
+          <t>Коробка 2-х клапановая фланцевая Ду80</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="D113" s="5" t="inlineStr"/>
       <c r="E113" s="7" t="inlineStr"/>
       <c r="F113" s="8" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>135.3</v>
+        <v>47.6</v>
       </c>
       <c r="H113" s="10" t="n">
-        <v>135</v>
+        <v>714</v>
       </c>
       <c r="I113" s="11" t="n"/>
       <c r="J113" s="11" t="n"/>
@@ -3720,26 +3702,22 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>Клапан Ду20/10</t>
+          <t>Коробка 2-х клапановая фланцевая Ду80</t>
         </is>
       </c>
       <c r="C114" s="5" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="D114" s="5" t="inlineStr"/>
-      <c r="E114" s="12" t="inlineStr">
-        <is>
-          <t>581-С6.73</t>
-        </is>
-      </c>
+      <c r="E114" s="7" t="inlineStr"/>
       <c r="F114" s="8" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G114" s="9" t="n">
-        <v>2.4</v>
+        <v>57.8</v>
       </c>
       <c r="H114" s="10" t="n">
-        <v>7</v>
+        <v>751</v>
       </c>
       <c r="I114" s="11" t="n"/>
       <c r="J114" s="11" t="n"/>
@@ -3750,26 +3728,22 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>Кланан Рр18-2 45/25</t>
-        </is>
-      </c>
-      <c r="C115" s="5" t="inlineStr"/>
-      <c r="D115" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="E115" s="12" t="inlineStr">
-        <is>
-          <t>2619802505</t>
-        </is>
-      </c>
+          <t>Коробка 3-х клап.фланцевая Ду80</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="D115" s="5" t="inlineStr"/>
+      <c r="E115" s="7" t="inlineStr"/>
       <c r="F115" s="8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>6.8</v>
+        <v>68</v>
       </c>
       <c r="H115" s="10" t="n">
-        <v>7</v>
+        <v>816</v>
       </c>
       <c r="I115" s="11" t="n"/>
       <c r="J115" s="11" t="n"/>
@@ -3780,24 +3754,22 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>Кланан Рр18-2 45/25</t>
-        </is>
-      </c>
-      <c r="C116" s="5" t="inlineStr"/>
+          <t>Коробка 3-х клап.фланцевая Ду80</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="n">
+        <v>80</v>
+      </c>
       <c r="D116" s="5" t="inlineStr"/>
-      <c r="E116" s="12" t="inlineStr">
-        <is>
-          <t>2619802505</t>
-        </is>
-      </c>
+      <c r="E116" s="7" t="inlineStr"/>
       <c r="F116" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G116" s="9" t="n">
-        <v>6.8</v>
+        <v>57.8</v>
       </c>
       <c r="H116" s="10" t="n">
-        <v>7</v>
+        <v>462</v>
       </c>
       <c r="I116" s="11" t="n"/>
       <c r="J116" s="11" t="n"/>
@@ -3808,24 +3780,30 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>Клапан</t>
-        </is>
-      </c>
-      <c r="C117" s="5" t="inlineStr"/>
-      <c r="D117" s="5" t="inlineStr"/>
+          <t>Коробка 3-х клап.фланцевая невозврат.Ду80 Ру6</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>587-182.126</t>
+          <t>526-03.097</t>
         </is>
       </c>
       <c r="F117" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>6.8</v>
+        <v>57.8</v>
       </c>
       <c r="H117" s="10" t="n">
-        <v>7</v>
+        <v>173</v>
       </c>
       <c r="I117" s="11" t="n"/>
       <c r="J117" s="11" t="n"/>
@@ -3836,143 +3814,143 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Судовая запорная арматура</t>
-        </is>
-      </c>
-      <c r="C118" s="5" t="inlineStr"/>
+          <t>Коробка 2-х клапановая фланцевая Ду50</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="n">
+        <v>50</v>
+      </c>
       <c r="D118" s="5" t="inlineStr"/>
       <c r="E118" s="7" t="inlineStr"/>
       <c r="F118" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G118" s="9" t="n">
-        <v>6.8</v>
+        <v>30</v>
       </c>
       <c r="H118" s="10" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="I118" s="11" t="n"/>
       <c r="J118" s="11" t="n"/>
     </row>
-    <row r="119" ht="22" customHeight="1">
-      <c r="A119" s="4" t="inlineStr">
-        <is>
-          <t>Коробки клапанные — 11 позиций  65 шт  3 490 кг</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="n"/>
-      <c r="C119" s="4" t="n"/>
-      <c r="D119" s="4" t="n"/>
-      <c r="E119" s="4" t="n"/>
-      <c r="F119" s="4" t="n"/>
-      <c r="G119" s="4" t="n"/>
-      <c r="H119" s="4" t="n"/>
-      <c r="I119" s="4" t="n"/>
-      <c r="J119" s="4" t="n"/>
+    <row r="119" ht="26" customHeight="1">
+      <c r="A119" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>Коробка 2-х клапановая фланцевая Ду50</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D119" s="5" t="inlineStr"/>
+      <c r="E119" s="7" t="inlineStr"/>
+      <c r="F119" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G119" s="9" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="H119" s="10" t="n">
+        <v>71</v>
+      </c>
+      <c r="I119" s="11" t="n"/>
+      <c r="J119" s="11" t="n"/>
     </row>
     <row r="120" ht="26" customHeight="1">
       <c r="A120" s="5" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая Ду100</t>
+          <t>Коробка 3-х клап.фланцевая Ду50</t>
         </is>
       </c>
       <c r="C120" s="5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D120" s="5" t="inlineStr"/>
       <c r="E120" s="7" t="inlineStr"/>
       <c r="F120" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G120" s="9" t="n">
-        <v>90.5</v>
+        <v>41</v>
       </c>
       <c r="H120" s="10" t="n">
-        <v>90</v>
+        <v>205</v>
       </c>
       <c r="I120" s="11" t="n"/>
       <c r="J120" s="11" t="n"/>
     </row>
     <row r="121" ht="26" customHeight="1">
       <c r="A121" s="5" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапановая фланцевая Ду80</t>
+          <t>Коробка 3-х клап.фланцевая Ду50</t>
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="D121" s="5" t="inlineStr"/>
       <c r="E121" s="7" t="inlineStr"/>
       <c r="F121" s="8" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G121" s="9" t="n">
-        <v>47.6</v>
+        <v>35.5</v>
       </c>
       <c r="H121" s="10" t="n">
-        <v>714</v>
+        <v>106</v>
       </c>
       <c r="I121" s="11" t="n"/>
       <c r="J121" s="11" t="n"/>
     </row>
     <row r="122" ht="26" customHeight="1">
       <c r="A122" s="5" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапановая фланцевая Ду80</t>
-        </is>
-      </c>
-      <c r="C122" s="5" t="n">
-        <v>80</v>
-      </c>
+          <t>Коробка 2-х клапанная корпус</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr"/>
       <c r="D122" s="5" t="inlineStr"/>
       <c r="E122" s="7" t="inlineStr"/>
       <c r="F122" s="8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G122" s="9" t="n">
-        <v>57.8</v>
+        <v>40</v>
       </c>
       <c r="H122" s="10" t="n">
-        <v>751</v>
+        <v>40</v>
       </c>
       <c r="I122" s="11" t="n"/>
       <c r="J122" s="11" t="n"/>
     </row>
-    <row r="123" ht="26" customHeight="1">
-      <c r="A123" s="5" t="n">
-        <v>111</v>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>Коробка 3-х клап.фланцевая Ду80</t>
-        </is>
-      </c>
-      <c r="C123" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="D123" s="5" t="inlineStr"/>
-      <c r="E123" s="7" t="inlineStr"/>
-      <c r="F123" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="G123" s="9" t="n">
-        <v>68</v>
-      </c>
-      <c r="H123" s="10" t="n">
-        <v>816</v>
-      </c>
-      <c r="I123" s="11" t="n"/>
-      <c r="J123" s="11" t="n"/>
+    <row r="123" ht="22" customHeight="1">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>Захлопки — 7 позиций  11 шт  204 кг</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="n"/>
+      <c r="C123" s="4" t="n"/>
+      <c r="D123" s="4" t="n"/>
+      <c r="E123" s="4" t="n"/>
+      <c r="F123" s="4" t="n"/>
+      <c r="G123" s="4" t="n"/>
+      <c r="H123" s="4" t="n"/>
+      <c r="I123" s="4" t="n"/>
+      <c r="J123" s="4" t="n"/>
     </row>
     <row r="124" ht="26" customHeight="1">
       <c r="A124" s="5" t="n">
@@ -3980,22 +3958,26 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая Ду80</t>
+          <t>Захлопка фланцевая вертикальная Ду100</t>
         </is>
       </c>
       <c r="C124" s="5" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D124" s="5" t="inlineStr"/>
-      <c r="E124" s="7" t="inlineStr"/>
+      <c r="E124" s="12" t="inlineStr">
+        <is>
+          <t>529-03.003</t>
+        </is>
+      </c>
       <c r="F124" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G124" s="9" t="n">
-        <v>57.8</v>
+        <v>33.7</v>
       </c>
       <c r="H124" s="10" t="n">
-        <v>462</v>
+        <v>34</v>
       </c>
       <c r="I124" s="11" t="n"/>
       <c r="J124" s="11" t="n"/>
@@ -4006,30 +3988,28 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая невозврат.Ду80 Ру6</t>
+          <t>Захлопка фланцевая горизон. Ду100 Ру10</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="D125" s="5" t="n">
+        <v>10</v>
       </c>
       <c r="E125" s="12" t="inlineStr">
         <is>
-          <t>526-03.097</t>
+          <t>529-03.074</t>
         </is>
       </c>
       <c r="F125" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>57.8</v>
+        <v>22</v>
       </c>
       <c r="H125" s="10" t="n">
-        <v>173</v>
+        <v>66</v>
       </c>
       <c r="I125" s="11" t="n"/>
       <c r="J125" s="11" t="n"/>
@@ -4040,22 +4020,28 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапановая фланцевая Ду50</t>
+          <t>Захлопка фланцевая проходная Ду100Ру6,3</t>
         </is>
       </c>
       <c r="C126" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="D126" s="5" t="inlineStr"/>
-      <c r="E126" s="7" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="D126" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E126" s="12" t="inlineStr">
+        <is>
+          <t>529-35.1406-01</t>
+        </is>
+      </c>
       <c r="F126" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G126" s="9" t="n">
-        <v>30</v>
+        <v>23.6</v>
       </c>
       <c r="H126" s="10" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="I126" s="11" t="n"/>
       <c r="J126" s="11" t="n"/>
@@ -4066,22 +4052,28 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапановая фланцевая Ду50</t>
+          <t>Захлопка фланцевая угловая Ду100Ру6,3</t>
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="D127" s="5" t="inlineStr"/>
-      <c r="E127" s="7" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="D127" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>529-35-1405-01</t>
+        </is>
+      </c>
       <c r="F127" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>35.5</v>
+        <v>26</v>
       </c>
       <c r="H127" s="10" t="n">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="I127" s="11" t="n"/>
       <c r="J127" s="11" t="n"/>
@@ -4092,22 +4084,26 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая Ду50</t>
+          <t>Захлопка Ду50Ру6 - БРАК</t>
         </is>
       </c>
       <c r="C128" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D128" s="5" t="inlineStr"/>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="E128" s="7" t="inlineStr"/>
       <c r="F128" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G128" s="9" t="n">
-        <v>41</v>
+        <v>10.8</v>
       </c>
       <c r="H128" s="10" t="n">
-        <v>205</v>
+        <v>33</v>
       </c>
       <c r="I128" s="11" t="n"/>
       <c r="J128" s="11" t="n"/>
@@ -4118,22 +4114,28 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая Ду50</t>
+          <t>Захлопка фланцевая вертикальная Ду50Ру63</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D129" s="5" t="inlineStr"/>
-      <c r="E129" s="7" t="inlineStr"/>
+      <c r="D129" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="E129" s="12" t="inlineStr">
+        <is>
+          <t>529-35.1400-01</t>
+        </is>
+      </c>
       <c r="F129" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>35.5</v>
+        <v>10.5</v>
       </c>
       <c r="H129" s="10" t="n">
-        <v>106</v>
+        <v>10</v>
       </c>
       <c r="I129" s="11" t="n"/>
       <c r="J129" s="11" t="n"/>
@@ -4144,20 +4146,26 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапанная корпус</t>
-        </is>
-      </c>
-      <c r="C130" s="5" t="inlineStr"/>
+          <t>Захлопка фланцевая горизонтальная Ду50</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="n">
+        <v>50</v>
+      </c>
       <c r="D130" s="5" t="inlineStr"/>
-      <c r="E130" s="7" t="inlineStr"/>
+      <c r="E130" s="12" t="inlineStr">
+        <is>
+          <t>529-03.011</t>
+        </is>
+      </c>
       <c r="F130" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G130" s="9" t="n">
-        <v>40</v>
+        <v>11.2</v>
       </c>
       <c r="H130" s="10" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="I130" s="11" t="n"/>
       <c r="J130" s="11" t="n"/>
@@ -4165,7 +4173,7 @@
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>Захлопки — 7 позиций  11 шт  204 кг</t>
+          <t>Кингстоны — 5 позиций  7 шт  100 кг</t>
         </is>
       </c>
       <c r="B131" s="4" t="n"/>
@@ -4184,26 +4192,28 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая вертикальная Ду100</t>
+          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
         </is>
       </c>
       <c r="C132" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="D132" s="5" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="D132" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="E132" s="12" t="inlineStr">
         <is>
-          <t>529-03.003</t>
+          <t>527-03.055</t>
         </is>
       </c>
       <c r="F132" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G132" s="9" t="n">
-        <v>33.7</v>
+        <v>19</v>
       </c>
       <c r="H132" s="10" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I132" s="11" t="n"/>
       <c r="J132" s="11" t="n"/>
@@ -4214,28 +4224,28 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая горизон. Ду100 Ру10</t>
+          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E133" s="12" t="inlineStr">
         <is>
-          <t>529-03.074</t>
+          <t>527-03.055</t>
         </is>
       </c>
       <c r="F133" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H133" s="10" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="I133" s="11" t="n"/>
       <c r="J133" s="11" t="n"/>
@@ -4246,28 +4256,28 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая проходная Ду100Ру6,3</t>
+          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
         </is>
       </c>
       <c r="C134" s="5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E134" s="12" t="inlineStr">
         <is>
-          <t>529-35.1406-01</t>
+          <t>527-03.054</t>
         </is>
       </c>
       <c r="F134" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G134" s="9" t="n">
-        <v>23.6</v>
+        <v>11</v>
       </c>
       <c r="H134" s="10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I134" s="11" t="n"/>
       <c r="J134" s="11" t="n"/>
@@ -4278,28 +4288,28 @@
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая угловая Ду100Ру6,3</t>
+          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E135" s="12" t="inlineStr">
         <is>
-          <t>529-35-1405-01</t>
+          <t>без чертежа(527-35.1165)</t>
         </is>
       </c>
       <c r="F135" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>26</v>
+        <v>9.4</v>
       </c>
       <c r="H135" s="10" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="I135" s="11" t="n"/>
       <c r="J135" s="11" t="n"/>
@@ -4310,107 +4320,107 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>Захлопка Ду50Ру6 - БРАК</t>
+          <t>Кингстон донный фланцевый Ду32Ру2,5</t>
         </is>
       </c>
       <c r="C136" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E136" s="7" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="D136" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E136" s="12" t="inlineStr">
+        <is>
+          <t>527-03.014</t>
+        </is>
+      </c>
       <c r="F136" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G136" s="9" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="H136" s="10" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="I136" s="11" t="n"/>
       <c r="J136" s="11" t="n"/>
     </row>
-    <row r="137" ht="26" customHeight="1">
-      <c r="A137" s="5" t="n">
-        <v>124</v>
-      </c>
-      <c r="B137" s="6" t="inlineStr">
-        <is>
-          <t>Захлопка фланцевая вертикальная Ду50Ру63</t>
-        </is>
-      </c>
-      <c r="C137" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="D137" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="E137" s="12" t="inlineStr">
-        <is>
-          <t>529-35.1400-01</t>
-        </is>
-      </c>
-      <c r="F137" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G137" s="9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="H137" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="I137" s="11" t="n"/>
-      <c r="J137" s="11" t="n"/>
+    <row r="137" ht="22" customHeight="1">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>Штуцерная  угол или проход не указан — 12 позиций  145 шт  263 кг</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="n"/>
+      <c r="C137" s="4" t="n"/>
+      <c r="D137" s="4" t="n"/>
+      <c r="E137" s="4" t="n"/>
+      <c r="F137" s="4" t="n"/>
+      <c r="G137" s="4" t="n"/>
+      <c r="H137" s="4" t="n"/>
+      <c r="I137" s="4" t="n"/>
+      <c r="J137" s="4" t="n"/>
     </row>
     <row r="138" ht="26" customHeight="1">
       <c r="A138" s="5" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая горизонтальная Ду50</t>
+          <t>Клапан запорн.с присоед.под дюрит прох. Ду65</t>
         </is>
       </c>
       <c r="C138" s="5" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D138" s="5" t="inlineStr"/>
       <c r="E138" s="12" t="inlineStr">
         <is>
-          <t>529-03.011</t>
+          <t>ИШТЛ 491112-003-04</t>
         </is>
       </c>
       <c r="F138" s="8" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G138" s="9" t="n">
-        <v>11.2</v>
+        <v>5.7</v>
       </c>
       <c r="H138" s="10" t="n">
-        <v>11</v>
+        <v>114</v>
       </c>
       <c r="I138" s="11" t="n"/>
       <c r="J138" s="11" t="n"/>
     </row>
-    <row r="139" ht="22" customHeight="1">
-      <c r="A139" s="4" t="inlineStr">
-        <is>
-          <t>Кингстоны — 5 позиций  7 шт  100 кг</t>
-        </is>
-      </c>
-      <c r="B139" s="4" t="n"/>
-      <c r="C139" s="4" t="n"/>
-      <c r="D139" s="4" t="n"/>
-      <c r="E139" s="4" t="n"/>
-      <c r="F139" s="4" t="n"/>
-      <c r="G139" s="4" t="n"/>
-      <c r="H139" s="4" t="n"/>
-      <c r="I139" s="4" t="n"/>
-      <c r="J139" s="4" t="n"/>
+    <row r="139" ht="26" customHeight="1">
+      <c r="A139" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D139" s="5" t="inlineStr"/>
+      <c r="E139" s="12" t="inlineStr">
+        <is>
+          <t>522-03.122-04</t>
+        </is>
+      </c>
+      <c r="F139" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G139" s="9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H139" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="I139" s="11" t="n"/>
+      <c r="J139" s="11" t="n"/>
     </row>
     <row r="140" ht="26" customHeight="1">
       <c r="A140" s="5" t="n">
@@ -4418,28 +4428,28 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
+          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50 Ру6</t>
         </is>
       </c>
       <c r="C140" s="5" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="D140" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E140" s="12" t="inlineStr">
+        <is>
+          <t>522-03.124-04</t>
+        </is>
+      </c>
+      <c r="F140" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H140" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="E140" s="12" t="inlineStr">
-        <is>
-          <t>527-03.055</t>
-        </is>
-      </c>
-      <c r="F140" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G140" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="H140" s="10" t="n">
-        <v>38</v>
       </c>
       <c r="I140" s="11" t="n"/>
       <c r="J140" s="11" t="n"/>
@@ -4450,28 +4460,28 @@
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
+          <t>Клапан предохранительный штуцерный сигнальный Ду10Ру1,3-6,5</t>
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E141" s="12" t="inlineStr">
         <is>
-          <t>527-03.055</t>
+          <t>524-03.174</t>
         </is>
       </c>
       <c r="F141" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>19</v>
+        <v>0.8</v>
       </c>
       <c r="H141" s="10" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="I141" s="11" t="n"/>
       <c r="J141" s="11" t="n"/>
@@ -4482,28 +4492,28 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
+          <t>Клапан предохранительный штуцерный сигнальный Ду10Ру2,5-6,5</t>
         </is>
       </c>
       <c r="C142" s="5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D142" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E142" s="12" t="inlineStr">
         <is>
-          <t>527-03.054</t>
+          <t>524-03.173</t>
         </is>
       </c>
       <c r="F142" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G142" s="9" t="n">
-        <v>11</v>
+        <v>1.2</v>
       </c>
       <c r="H142" s="10" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="I142" s="11" t="n"/>
       <c r="J142" s="11" t="n"/>
@@ -4514,28 +4524,30 @@
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
+          <t>Клапан для манометра штущерный сальниковый Ду6Ру100 б/у</t>
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="D143" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="E143" s="12" t="inlineStr">
         <is>
-          <t>без чертежа(527-35.1165)</t>
+          <t>521-02.013</t>
         </is>
       </c>
       <c r="F143" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>9.4</v>
+        <v>0.7</v>
       </c>
       <c r="H143" s="10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I143" s="11" t="n"/>
       <c r="J143" s="11" t="n"/>
@@ -4546,133 +4558,157 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду32Ру2,5</t>
+          <t>Клапан для манометра штущерный сальниковый Ду6Ру100 б/у</t>
         </is>
       </c>
       <c r="C144" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="D144" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="E144" s="12" t="inlineStr">
         <is>
-          <t>527-03.014</t>
+          <t>521-02.014</t>
         </is>
       </c>
       <c r="F144" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G144" s="9" t="n">
-        <v>11.2</v>
+        <v>0.7</v>
       </c>
       <c r="H144" s="10" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I144" s="11" t="n"/>
       <c r="J144" s="11" t="n"/>
     </row>
-    <row r="145" ht="22" customHeight="1">
-      <c r="A145" s="4" t="inlineStr">
-        <is>
-          <t>Штуцерная  угол или проход не указан — 12 позиций  145 шт  263 кг</t>
-        </is>
-      </c>
-      <c r="B145" s="4" t="n"/>
-      <c r="C145" s="4" t="n"/>
-      <c r="D145" s="4" t="n"/>
-      <c r="E145" s="4" t="n"/>
-      <c r="F145" s="4" t="n"/>
-      <c r="G145" s="4" t="n"/>
-      <c r="H145" s="4" t="n"/>
-      <c r="I145" s="4" t="n"/>
-      <c r="J145" s="4" t="n"/>
+    <row r="145" ht="26" customHeight="1">
+      <c r="A145" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>Клапан для манометра штущерный сальниковый Ду6Ру100 новый</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E145" s="12" t="inlineStr">
+        <is>
+          <t>521-02.013</t>
+        </is>
+      </c>
+      <c r="F145" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="G145" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H145" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="I145" s="11" t="n"/>
+      <c r="J145" s="11" t="n"/>
     </row>
     <row r="146" ht="26" customHeight="1">
       <c r="A146" s="5" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>Клапан запорн.с присоед.под дюрит прох. Ду65</t>
+          <t>Клапан предохранительный штуцерный сигнальный Ду6 Ру100-230</t>
         </is>
       </c>
       <c r="C146" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="D146" s="5" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="D146" s="5" t="n">
+        <v>100</v>
+      </c>
       <c r="E146" s="12" t="inlineStr">
         <is>
-          <t>ИШТЛ 491112-003-04</t>
+          <t>524-35.2423-01</t>
         </is>
       </c>
       <c r="F146" s="8" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G146" s="9" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="H146" s="10" t="n">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="I146" s="11" t="n"/>
       <c r="J146" s="11" t="n"/>
     </row>
     <row r="147" ht="26" customHeight="1">
       <c r="A147" s="5" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50</t>
+          <t>Клапан предохранительный штуцерный сигнальный Ду6Ру100-250</t>
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="D147" s="5" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="D147" s="5" t="n">
+        <v>100</v>
+      </c>
       <c r="E147" s="12" t="inlineStr">
         <is>
-          <t>522-03.122-04</t>
+          <t>524-03.188</t>
         </is>
       </c>
       <c r="F147" s="8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="H147" s="10" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="I147" s="11" t="n"/>
       <c r="J147" s="11" t="n"/>
     </row>
     <row r="148" ht="26" customHeight="1">
       <c r="A148" s="5" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50 Ру6</t>
+          <t>Клапан для манометра штущерный  Ду3Ру400 новый</t>
         </is>
       </c>
       <c r="C148" s="5" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>6</v>
+        <v>400</v>
       </c>
       <c r="E148" s="12" t="inlineStr">
         <is>
-          <t>522-03.124-04</t>
+          <t>521-03.406</t>
         </is>
       </c>
       <c r="F148" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G148" s="9" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="H148" s="10" t="n">
         <v>2</v>
@@ -4682,67 +4718,47 @@
     </row>
     <row r="149" ht="26" customHeight="1">
       <c r="A149" s="5" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду10Ру1,3-6,5</t>
-        </is>
-      </c>
-      <c r="C149" s="5" t="n">
+          <t>Клапан для манометра штуцерный сальниковый</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr"/>
+      <c r="D149" s="5" t="inlineStr"/>
+      <c r="E149" s="12" t="inlineStr">
+        <is>
+          <t>521-34.3404-03</t>
+        </is>
+      </c>
+      <c r="F149" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="D149" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E149" s="12" t="inlineStr">
-        <is>
-          <t>524-03.174</t>
-        </is>
-      </c>
-      <c r="F149" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="G149" s="9" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="H149" s="10" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I149" s="11" t="n"/>
       <c r="J149" s="11" t="n"/>
     </row>
-    <row r="150" ht="26" customHeight="1">
-      <c r="A150" s="5" t="n">
-        <v>135</v>
-      </c>
-      <c r="B150" s="6" t="inlineStr">
-        <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду10Ру2,5-6,5</t>
-        </is>
-      </c>
-      <c r="C150" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D150" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E150" s="12" t="inlineStr">
-        <is>
-          <t>524-03.173</t>
-        </is>
-      </c>
-      <c r="F150" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G150" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H150" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I150" s="11" t="n"/>
-      <c r="J150" s="11" t="n"/>
+    <row r="150" ht="22" customHeight="1">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>Фланцевая  угол или проход не указан — 3 позиции  9 шт  106 кг</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="n"/>
+      <c r="C150" s="4" t="n"/>
+      <c r="D150" s="4" t="n"/>
+      <c r="E150" s="4" t="n"/>
+      <c r="F150" s="4" t="n"/>
+      <c r="G150" s="4" t="n"/>
+      <c r="H150" s="4" t="n"/>
+      <c r="I150" s="4" t="n"/>
+      <c r="J150" s="4" t="n"/>
     </row>
     <row r="151" ht="26" customHeight="1">
       <c r="A151" s="5" t="n">
@@ -4750,30 +4766,26 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>Клапан для манометра штущерный сальниковый Ду6Ру100 б/у</t>
+          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E151" s="12" t="inlineStr">
-        <is>
-          <t>521-02.013</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="inlineStr"/>
       <c r="F151" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>0.7</v>
+        <v>17</v>
       </c>
       <c r="H151" s="10" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="I151" s="11" t="n"/>
       <c r="J151" s="11" t="n"/>
@@ -4784,30 +4796,26 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>Клапан для манометра штущерный сальниковый Ду6Ру100 б/у</t>
+          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-35.4044-01)</t>
         </is>
       </c>
       <c r="C152" s="5" t="n">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E152" s="12" t="inlineStr">
-        <is>
-          <t>521-02.014</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr"/>
       <c r="F152" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G152" s="9" t="n">
-        <v>0.7</v>
+        <v>17</v>
       </c>
       <c r="H152" s="10" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I152" s="11" t="n"/>
       <c r="J152" s="11" t="n"/>
@@ -4818,279 +4826,281 @@
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>Клапан для манометра штущерный сальниковый Ду6Ру100 новый</t>
+          <t>Клапан невозвратно-приемный фланцевый Ду 50 Ру1 (522-35.4043-01)</t>
         </is>
       </c>
       <c r="C153" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E153" s="7" t="inlineStr"/>
+      <c r="F153" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D153" s="5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E153" s="12" t="inlineStr">
-        <is>
-          <t>521-02.013</t>
-        </is>
-      </c>
-      <c r="F153" s="8" t="n">
-        <v>95</v>
-      </c>
       <c r="G153" s="9" t="n">
-        <v>0.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H153" s="10" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="I153" s="11" t="n"/>
       <c r="J153" s="11" t="n"/>
     </row>
-    <row r="154" ht="26" customHeight="1">
-      <c r="A154" s="5" t="n">
-        <v>139</v>
-      </c>
-      <c r="B154" s="6" t="inlineStr">
-        <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду6 Ру100-230</t>
-        </is>
-      </c>
-      <c r="C154" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D154" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E154" s="12" t="inlineStr">
-        <is>
-          <t>524-35.2423-01</t>
-        </is>
-      </c>
-      <c r="F154" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G154" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H154" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="I154" s="11" t="n"/>
-      <c r="J154" s="11" t="n"/>
+    <row r="154" ht="22" customHeight="1">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>Паровые клапаны — 1 позиция  1 шт  33 кг</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="n"/>
+      <c r="C154" s="4" t="n"/>
+      <c r="D154" s="4" t="n"/>
+      <c r="E154" s="4" t="n"/>
+      <c r="F154" s="4" t="n"/>
+      <c r="G154" s="4" t="n"/>
+      <c r="H154" s="4" t="n"/>
+      <c r="I154" s="4" t="n"/>
+      <c r="J154" s="4" t="n"/>
     </row>
     <row r="155" ht="26" customHeight="1">
       <c r="A155" s="5" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду6Ру100-250</t>
+          <t>Клапан паровой Ду65Ру10</t>
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="E155" s="12" t="inlineStr">
         <is>
-          <t>524-03.188</t>
+          <t>581-03.034</t>
         </is>
       </c>
       <c r="F155" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>2.1</v>
+        <v>32.6</v>
       </c>
       <c r="H155" s="10" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="I155" s="11" t="n"/>
       <c r="J155" s="11" t="n"/>
     </row>
-    <row r="156" ht="26" customHeight="1">
-      <c r="A156" s="5" t="n">
-        <v>141</v>
-      </c>
-      <c r="B156" s="6" t="inlineStr">
-        <is>
-          <t>Клапан для манометра штущерный  Ду3Ру400 новый</t>
-        </is>
-      </c>
-      <c r="C156" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D156" s="5" t="n">
-        <v>400</v>
-      </c>
-      <c r="E156" s="12" t="inlineStr">
-        <is>
-          <t>521-03.406</t>
-        </is>
-      </c>
-      <c r="F156" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G156" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H156" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="I156" s="11" t="n"/>
-      <c r="J156" s="11" t="n"/>
+    <row r="156" ht="22" customHeight="1">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая — 48 позиций  251 шт  666 кг</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="n"/>
+      <c r="C156" s="4" t="n"/>
+      <c r="D156" s="4" t="n"/>
+      <c r="E156" s="4" t="n"/>
+      <c r="F156" s="4" t="n"/>
+      <c r="G156" s="4" t="n"/>
+      <c r="H156" s="4" t="n"/>
+      <c r="I156" s="4" t="n"/>
+      <c r="J156" s="4" t="n"/>
     </row>
     <row r="157" ht="26" customHeight="1">
       <c r="A157" s="5" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>Клапан для манометра штуцерный сальниковый</t>
-        </is>
-      </c>
-      <c r="C157" s="5" t="inlineStr"/>
-      <c r="D157" s="5" t="inlineStr"/>
+          <t>Клапан угловой с присоединением под дюрит Ду50Ру4</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D157" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="E157" s="12" t="inlineStr">
         <is>
-          <t>521-34.3404-03</t>
+          <t>521-03.445-04</t>
         </is>
       </c>
       <c r="F157" s="8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G157" s="9" t="n">
         <v>1.3</v>
       </c>
       <c r="H157" s="10" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I157" s="11" t="n"/>
       <c r="J157" s="11" t="n"/>
     </row>
-    <row r="158" ht="22" customHeight="1">
-      <c r="A158" s="4" t="inlineStr">
-        <is>
-          <t>Фланцевая  угол или проход не указан — 3 позиции  9 шт  106 кг</t>
-        </is>
-      </c>
-      <c r="B158" s="4" t="n"/>
-      <c r="C158" s="4" t="n"/>
-      <c r="D158" s="4" t="n"/>
-      <c r="E158" s="4" t="n"/>
-      <c r="F158" s="4" t="n"/>
-      <c r="G158" s="4" t="n"/>
-      <c r="H158" s="4" t="n"/>
-      <c r="I158" s="4" t="n"/>
-      <c r="J158" s="4" t="n"/>
+    <row r="158" ht="26" customHeight="1">
+      <c r="A158" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду32</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="D158" s="5" t="inlineStr"/>
+      <c r="E158" s="7" t="inlineStr"/>
+      <c r="F158" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G158" s="9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H158" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="I158" s="11" t="n"/>
+      <c r="J158" s="11" t="n"/>
     </row>
     <row r="159" ht="26" customHeight="1">
       <c r="A159" s="5" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
+          <t>Клапан штуцерный угловой Ду32 Ру100</t>
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E159" s="7" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E159" s="12" t="inlineStr">
+        <is>
+          <t>521-01.468-07</t>
+        </is>
+      </c>
       <c r="F159" s="8" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>17</v>
+        <v>3.3</v>
       </c>
       <c r="H159" s="10" t="n">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="I159" s="11" t="n"/>
       <c r="J159" s="11" t="n"/>
     </row>
     <row r="160" ht="26" customHeight="1">
       <c r="A160" s="5" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-35.4044-01)</t>
+          <t>Клапан штуцерный угловой Ду32Ру100</t>
         </is>
       </c>
       <c r="C160" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="D160" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E160" s="7" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="D160" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E160" s="12" t="inlineStr">
+        <is>
+          <t>521-01.468-07</t>
+        </is>
+      </c>
       <c r="F160" s="8" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="G160" s="9" t="n">
-        <v>17</v>
+        <v>3.3</v>
       </c>
       <c r="H160" s="10" t="n">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c r="I160" s="11" t="n"/>
       <c r="J160" s="11" t="n"/>
     </row>
     <row r="161" ht="26" customHeight="1">
       <c r="A161" s="5" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 50 Ру1 (522-35.4043-01)</t>
+          <t>Клапан штуцерный угловой Ду32Ру100</t>
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="D161" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E161" s="7" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="D161" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E161" s="12" t="inlineStr">
+        <is>
+          <t>521-01.464-07</t>
+        </is>
+      </c>
       <c r="F161" s="8" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>9.199999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="H161" s="10" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="I161" s="11" t="n"/>
       <c r="J161" s="11" t="n"/>
     </row>
-    <row r="162" ht="22" customHeight="1">
-      <c r="A162" s="4" t="inlineStr">
-        <is>
-          <t>Паровые клапаны — 1 позиция  1 шт  33 кг</t>
-        </is>
-      </c>
-      <c r="B162" s="4" t="n"/>
-      <c r="C162" s="4" t="n"/>
-      <c r="D162" s="4" t="n"/>
-      <c r="E162" s="4" t="n"/>
-      <c r="F162" s="4" t="n"/>
-      <c r="G162" s="4" t="n"/>
-      <c r="H162" s="4" t="n"/>
-      <c r="I162" s="4" t="n"/>
-      <c r="J162" s="4" t="n"/>
+    <row r="162" ht="26" customHeight="1">
+      <c r="A162" s="5" t="n">
+        <v>145</v>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду32Ру100</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="D162" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E162" s="12" t="inlineStr">
+        <is>
+          <t>521-01.464-06</t>
+        </is>
+      </c>
+      <c r="F162" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G162" s="9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H162" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I162" s="11" t="n"/>
+      <c r="J162" s="11" t="n"/>
     </row>
     <row r="163" ht="26" customHeight="1">
       <c r="A163" s="5" t="n">
@@ -5098,113 +5108,141 @@
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>Клапан паровой Ду65Ру10</t>
+          <t>Клапан штуцерный угловой Ду32Ру100</t>
         </is>
       </c>
       <c r="C163" s="5" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E163" s="12" t="inlineStr">
         <is>
-          <t>581-03.034</t>
+          <t>522-01.500-07</t>
         </is>
       </c>
       <c r="F163" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>32.6</v>
+        <v>3.3</v>
       </c>
       <c r="H163" s="10" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="I163" s="11" t="n"/>
       <c r="J163" s="11" t="n"/>
     </row>
-    <row r="164" ht="22" customHeight="1">
-      <c r="A164" s="4" t="inlineStr">
-        <is>
-          <t>Штуцерная угловая — 48 позиций  251 шт  666 кг</t>
-        </is>
-      </c>
-      <c r="B164" s="4" t="n"/>
-      <c r="C164" s="4" t="n"/>
-      <c r="D164" s="4" t="n"/>
-      <c r="E164" s="4" t="n"/>
-      <c r="F164" s="4" t="n"/>
-      <c r="G164" s="4" t="n"/>
-      <c r="H164" s="4" t="n"/>
-      <c r="I164" s="4" t="n"/>
-      <c r="J164" s="4" t="n"/>
+    <row r="164" ht="26" customHeight="1">
+      <c r="A164" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="B164" s="6" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E164" s="12" t="inlineStr">
+        <is>
+          <t>521-01.464-07</t>
+        </is>
+      </c>
+      <c r="F164" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="G164" s="9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H164" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="I164" s="11" t="n"/>
+      <c r="J164" s="11" t="n"/>
     </row>
     <row r="165" ht="26" customHeight="1">
       <c r="A165" s="5" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>Клапан угловой с присоединением под дюрит Ду50Ру4</t>
+          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
         </is>
       </c>
       <c r="C165" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="D165" s="5" t="n">
-        <v>4</v>
+        <v>32</v>
+      </c>
+      <c r="D165" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="E165" s="12" t="inlineStr">
         <is>
-          <t>521-03.445-04</t>
+          <t>521-01.464-06</t>
         </is>
       </c>
       <c r="F165" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="H165" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I165" s="11" t="n"/>
       <c r="J165" s="11" t="n"/>
     </row>
     <row r="166" ht="26" customHeight="1">
       <c r="A166" s="5" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32</t>
+          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
         </is>
       </c>
       <c r="C166" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="D166" s="5" t="inlineStr"/>
-      <c r="E166" s="7" t="inlineStr"/>
+      <c r="D166" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E166" s="12" t="inlineStr">
+        <is>
+          <t>522-01.500-07</t>
+        </is>
+      </c>
       <c r="F166" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G166" s="9" t="n">
         <v>3.3</v>
       </c>
       <c r="H166" s="10" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="I166" s="11" t="n"/>
       <c r="J166" s="11" t="n"/>
     </row>
     <row r="167" ht="26" customHeight="1">
       <c r="A167" s="5" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32 Ру100</t>
+          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
         </is>
       </c>
       <c r="C167" s="5" t="n">
@@ -5221,138 +5259,128 @@
         </is>
       </c>
       <c r="F167" s="8" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G167" s="9" t="n">
         <v>3.3</v>
       </c>
       <c r="H167" s="10" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I167" s="11" t="n"/>
       <c r="J167" s="11" t="n"/>
     </row>
     <row r="168" ht="26" customHeight="1">
       <c r="A168" s="5" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32Ру100</t>
+          <t>Клапан штуцерный угловой Ду25</t>
         </is>
       </c>
       <c r="C168" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="D168" s="5" t="n">
-        <v>100</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="D168" s="5" t="inlineStr"/>
       <c r="E168" s="12" t="inlineStr">
         <is>
-          <t>521-01.468-07</t>
+          <t>521--01.468-08</t>
         </is>
       </c>
       <c r="F168" s="8" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="G168" s="9" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="H168" s="10" t="n">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="I168" s="11" t="n"/>
       <c r="J168" s="11" t="n"/>
     </row>
     <row r="169" ht="26" customHeight="1">
       <c r="A169" s="5" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32Ру100</t>
+          <t>Клапан штуцерный угловой Ду25</t>
         </is>
       </c>
       <c r="C169" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="D169" s="5" t="n">
-        <v>100</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="D169" s="5" t="inlineStr"/>
       <c r="E169" s="12" t="inlineStr">
         <is>
-          <t>521-01.464-07</t>
+          <t>521--35.3363</t>
         </is>
       </c>
       <c r="F169" s="8" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="H169" s="10" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="I169" s="11" t="n"/>
       <c r="J169" s="11" t="n"/>
     </row>
     <row r="170" ht="26" customHeight="1">
       <c r="A170" s="5" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32Ру100</t>
+          <t>Клапан штуцерный угловой Ду25</t>
         </is>
       </c>
       <c r="C170" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="D170" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E170" s="12" t="inlineStr">
-        <is>
-          <t>521-01.464-06</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="D170" s="5" t="inlineStr"/>
+      <c r="E170" s="7" t="inlineStr"/>
       <c r="F170" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G170" s="9" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="H170" s="10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I170" s="11" t="n"/>
       <c r="J170" s="11" t="n"/>
     </row>
     <row r="171" ht="26" customHeight="1">
       <c r="A171" s="5" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32Ру100</t>
+          <t>Клапан штуцерный угловой Ду25 Ру 100</t>
         </is>
       </c>
       <c r="C171" s="5" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D171" s="5" t="n">
         <v>100</v>
       </c>
       <c r="E171" s="12" t="inlineStr">
         <is>
-          <t>522-01.500-07</t>
+          <t>521--35.3363</t>
         </is>
       </c>
       <c r="F171" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="H171" s="10" t="n">
         <v>3</v>
@@ -5362,15 +5390,15 @@
     </row>
     <row r="172" ht="26" customHeight="1">
       <c r="A172" s="5" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
+          <t>Клапан штуцерный угловой Ду25 Ру100</t>
         </is>
       </c>
       <c r="C172" s="5" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
@@ -5379,100 +5407,98 @@
       </c>
       <c r="E172" s="12" t="inlineStr">
         <is>
-          <t>521-01.464-07</t>
+          <t>521-01.468-06</t>
         </is>
       </c>
       <c r="F172" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G172" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H172" s="10" t="n">
         <v>14</v>
-      </c>
-      <c r="G172" s="9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H172" s="10" t="n">
-        <v>46</v>
       </c>
       <c r="I172" s="11" t="n"/>
       <c r="J172" s="11" t="n"/>
     </row>
     <row r="173" ht="26" customHeight="1">
       <c r="A173" s="5" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
+          <t>Клапан невозв-запор.цапковый угловой  под дюрит Ду20Ру6</t>
         </is>
       </c>
       <c r="C173" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="D173" s="5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="D173" s="5" t="n">
+        <v>6</v>
       </c>
       <c r="E173" s="12" t="inlineStr">
         <is>
-          <t>521-01.464-06</t>
+          <t>522-03.123</t>
         </is>
       </c>
       <c r="F173" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="H173" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I173" s="11" t="n"/>
       <c r="J173" s="11" t="n"/>
     </row>
     <row r="174" ht="26" customHeight="1">
       <c r="A174" s="5" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
+          <t>Клапан невозв-запор.цапковый угловой под дюрит Ду20Ру6</t>
         </is>
       </c>
       <c r="C174" s="5" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E174" s="12" t="inlineStr">
         <is>
-          <t>522-01.500-07</t>
+          <t>522-03.123</t>
         </is>
       </c>
       <c r="F174" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G174" s="9" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="H174" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I174" s="11" t="n"/>
       <c r="J174" s="11" t="n"/>
     </row>
     <row r="175" ht="26" customHeight="1">
       <c r="A175" s="5" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
+          <t>Клапан штуцерный угловой Ду20 Ру100</t>
         </is>
       </c>
       <c r="C175" s="5" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
@@ -5481,37 +5507,39 @@
       </c>
       <c r="E175" s="12" t="inlineStr">
         <is>
-          <t>521-01.468-07</t>
+          <t>521-01.468-05</t>
         </is>
       </c>
       <c r="F175" s="8" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="H175" s="10" t="n">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c r="I175" s="11" t="n"/>
       <c r="J175" s="11" t="n"/>
     </row>
     <row r="176" ht="26" customHeight="1">
       <c r="A176" s="5" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду25</t>
+          <t>Клапан штуцерный угловой Ду20 Ру160</t>
         </is>
       </c>
       <c r="C176" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="D176" s="5" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="D176" s="5" t="n">
+        <v>160</v>
+      </c>
       <c r="E176" s="12" t="inlineStr">
         <is>
-          <t>521--01.468-08</t>
+          <t>521-03.479</t>
         </is>
       </c>
       <c r="F176" s="8" t="n">
@@ -5528,27 +5556,31 @@
     </row>
     <row r="177" ht="26" customHeight="1">
       <c r="A177" s="5" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду25</t>
+          <t>Клапан штуцерный угловой Ду20 Ру160</t>
         </is>
       </c>
       <c r="C177" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="D177" s="5" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="D177" s="5" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
       <c r="E177" s="12" t="inlineStr">
         <is>
-          <t>521--35.3363</t>
+          <t>521-03.479</t>
         </is>
       </c>
       <c r="F177" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="H177" s="10" t="n">
         <v>2</v>
@@ -5558,173 +5590,169 @@
     </row>
     <row r="178" ht="26" customHeight="1">
       <c r="A178" s="5" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду25</t>
+          <t>Клапан штуцерный угловой Ду20 ру 40</t>
         </is>
       </c>
       <c r="C178" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="D178" s="5" t="inlineStr"/>
-      <c r="E178" s="7" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="D178" s="5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E178" s="12" t="inlineStr">
+        <is>
+          <t>521-01.465-03</t>
+        </is>
+      </c>
       <c r="F178" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G178" s="9" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="H178" s="10" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I178" s="11" t="n"/>
       <c r="J178" s="11" t="n"/>
     </row>
     <row r="179" ht="26" customHeight="1">
       <c r="A179" s="5" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду25 Ру 100</t>
+          <t>Клапан штуцерный угловой Ду20 ру 40</t>
         </is>
       </c>
       <c r="C179" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="D179" s="5" t="n">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="D179" s="5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="E179" s="12" t="inlineStr">
         <is>
-          <t>521--35.3363</t>
+          <t>522-35.3632</t>
         </is>
       </c>
       <c r="F179" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="H179" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I179" s="11" t="n"/>
       <c r="J179" s="11" t="n"/>
     </row>
     <row r="180" ht="26" customHeight="1">
       <c r="A180" s="5" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду25 Ру100</t>
+          <t>Клапан штуцерный угловой Ду 15</t>
         </is>
       </c>
       <c r="C180" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="D180" s="5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="D180" s="5" t="inlineStr"/>
       <c r="E180" s="12" t="inlineStr">
         <is>
-          <t>521-01.468-06</t>
+          <t>521--01.468-08</t>
         </is>
       </c>
       <c r="F180" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G180" s="9" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="H180" s="10" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I180" s="11" t="n"/>
       <c r="J180" s="11" t="n"/>
     </row>
     <row r="181" ht="26" customHeight="1">
       <c r="A181" s="5" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>Клапан невозв-запор.цапковый угловой  под дюрит Ду20Ру6</t>
+          <t>Клапан штуцерный угловой Ду 15 НЕРЖ</t>
         </is>
       </c>
       <c r="C181" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D181" s="5" t="n">
-        <v>6</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="D181" s="5" t="inlineStr"/>
       <c r="E181" s="12" t="inlineStr">
         <is>
-          <t>522-03.123</t>
+          <t>521-03.478-01</t>
         </is>
       </c>
       <c r="F181" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="H181" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I181" s="11" t="n"/>
       <c r="J181" s="11" t="n"/>
     </row>
     <row r="182" ht="26" customHeight="1">
       <c r="A182" s="5" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>Клапан невозв-запор.цапковый угловой под дюрит Ду20Ру6</t>
+          <t>Клапан штуцерный угловой Ду15</t>
         </is>
       </c>
       <c r="C182" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D182" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E182" s="12" t="inlineStr">
-        <is>
-          <t>522-03.123</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="D182" s="5" t="inlineStr"/>
+      <c r="E182" s="7" t="inlineStr"/>
       <c r="F182" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G182" s="9" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="H182" s="10" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="I182" s="11" t="n"/>
       <c r="J182" s="11" t="n"/>
     </row>
     <row r="183" ht="26" customHeight="1">
       <c r="A183" s="5" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду20 Ру100</t>
+          <t>Клапан штуцерный угловой Ду15 Ру100</t>
         </is>
       </c>
       <c r="C183" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
@@ -5737,244 +5765,260 @@
         </is>
       </c>
       <c r="F183" s="8" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="H183" s="10" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="I183" s="11" t="n"/>
       <c r="J183" s="11" t="n"/>
     </row>
     <row r="184" ht="26" customHeight="1">
       <c r="A184" s="5" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду20 Ру160</t>
+          <t>Клапан штуцерный угловой Ду15 Ру100</t>
         </is>
       </c>
       <c r="C184" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D184" s="5" t="n">
-        <v>160</v>
+        <v>15</v>
+      </c>
+      <c r="D184" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="E184" s="12" t="inlineStr">
         <is>
-          <t>521-03.479</t>
+          <t>521-35.3362</t>
         </is>
       </c>
       <c r="F184" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G184" s="9" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="H184" s="10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I184" s="11" t="n"/>
       <c r="J184" s="11" t="n"/>
     </row>
     <row r="185" ht="26" customHeight="1">
       <c r="A185" s="5" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду20 Ру160</t>
+          <t>Клапан штуцерный угловой Ду15 Ру100</t>
         </is>
       </c>
       <c r="C185" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E185" s="12" t="inlineStr">
         <is>
-          <t>521-03.479</t>
+          <t>521-01.464-02</t>
         </is>
       </c>
       <c r="F185" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G185" s="9" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="H185" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I185" s="11" t="n"/>
       <c r="J185" s="11" t="n"/>
     </row>
     <row r="186" ht="26" customHeight="1">
       <c r="A186" s="5" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду20 ру 40</t>
+          <t>Клапан штуцерный угловой Ду15 Ру100</t>
         </is>
       </c>
       <c r="C186" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E186" s="12" t="inlineStr">
         <is>
-          <t>521-01.465-03</t>
+          <t>522-01.500-05</t>
         </is>
       </c>
       <c r="F186" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G186" s="9" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="H186" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I186" s="11" t="n"/>
       <c r="J186" s="11" t="n"/>
     </row>
     <row r="187" ht="26" customHeight="1">
       <c r="A187" s="5" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду20 ру 40</t>
+          <t>Клапан штуцерный угловой Ду15 Ру160</t>
         </is>
       </c>
       <c r="C187" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D187" s="5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="D187" s="5" t="n">
+        <v>160</v>
       </c>
       <c r="E187" s="12" t="inlineStr">
         <is>
-          <t>522-35.3632</t>
+          <t>521-03.387</t>
         </is>
       </c>
       <c r="F187" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G187" s="9" t="n">
-        <v>1.9</v>
+        <v>4.3</v>
       </c>
       <c r="H187" s="10" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I187" s="11" t="n"/>
       <c r="J187" s="11" t="n"/>
     </row>
     <row r="188" ht="26" customHeight="1">
       <c r="A188" s="5" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду 15</t>
+          <t>Клапан штуцерный угловой Ду15 Ру160</t>
         </is>
       </c>
       <c r="C188" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="D188" s="5" t="inlineStr"/>
+      <c r="D188" s="5" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
       <c r="E188" s="12" t="inlineStr">
         <is>
-          <t>521--01.468-08</t>
+          <t>521-03.387</t>
         </is>
       </c>
       <c r="F188" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G188" s="9" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="H188" s="10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I188" s="11" t="n"/>
       <c r="J188" s="11" t="n"/>
     </row>
     <row r="189" ht="26" customHeight="1">
       <c r="A189" s="5" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду 15 НЕРЖ</t>
+          <t>Клапан штуцерный угловой Ду15Ру100</t>
         </is>
       </c>
       <c r="C189" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="D189" s="5" t="inlineStr"/>
+      <c r="D189" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="E189" s="12" t="inlineStr">
         <is>
-          <t>521-03.478-01</t>
+          <t>522-01.500-04</t>
         </is>
       </c>
       <c r="F189" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G189" s="9" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="H189" s="10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I189" s="11" t="n"/>
       <c r="J189" s="11" t="n"/>
     </row>
     <row r="190" ht="26" customHeight="1">
       <c r="A190" s="5" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15</t>
+          <t>Клапан штуцерный угловой Ду15Ру100</t>
         </is>
       </c>
       <c r="C190" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="D190" s="5" t="inlineStr"/>
-      <c r="E190" s="7" t="inlineStr"/>
+      <c r="D190" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E190" s="12" t="inlineStr">
+        <is>
+          <t>521-01.464-01</t>
+        </is>
+      </c>
       <c r="F190" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G190" s="9" t="n">
         <v>2.6</v>
       </c>
       <c r="H190" s="10" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I190" s="11" t="n"/>
       <c r="J190" s="11" t="n"/>
     </row>
     <row r="191" ht="26" customHeight="1">
       <c r="A191" s="5" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15 Ру100</t>
+          <t>Клапан штуцерный угловой Ду15Ру100</t>
         </is>
       </c>
       <c r="C191" s="5" t="n">
@@ -5987,28 +6031,28 @@
       </c>
       <c r="E191" s="12" t="inlineStr">
         <is>
-          <t>521-01.468-05</t>
+          <t>521-01.468</t>
         </is>
       </c>
       <c r="F191" s="8" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G191" s="9" t="n">
         <v>2.6</v>
       </c>
       <c r="H191" s="10" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="I191" s="11" t="n"/>
       <c r="J191" s="11" t="n"/>
     </row>
     <row r="192" ht="26" customHeight="1">
       <c r="A192" s="5" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15 Ру100</t>
+          <t>Клапан штуцерный угловой Ду15Ру40</t>
         </is>
       </c>
       <c r="C192" s="5" t="n">
@@ -6016,12 +6060,12 @@
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E192" s="12" t="inlineStr">
         <is>
-          <t>521-35.3362</t>
+          <t>521-01.465-02</t>
         </is>
       </c>
       <c r="F192" s="8" t="n">
@@ -6038,149 +6082,145 @@
     </row>
     <row r="193" ht="26" customHeight="1">
       <c r="A193" s="5" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15 Ру100</t>
+          <t>Клапан штуцерный угловой Ду10 Р160</t>
         </is>
       </c>
       <c r="C193" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D193" s="5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="D193" s="5" t="n">
+        <v>160</v>
       </c>
       <c r="E193" s="12" t="inlineStr">
         <is>
-          <t>521-01.464-02</t>
+          <t>522-03.149</t>
         </is>
       </c>
       <c r="F193" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G193" s="9" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="H193" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I193" s="11" t="n"/>
       <c r="J193" s="11" t="n"/>
     </row>
     <row r="194" ht="26" customHeight="1">
       <c r="A194" s="5" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15 Ру100</t>
+          <t>Клапан штуцерный угловой Ду10 Р160</t>
         </is>
       </c>
       <c r="C194" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D194" s="5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D194" s="5" t="inlineStr"/>
       <c r="E194" s="12" t="inlineStr">
         <is>
-          <t>522-01.500-05</t>
+          <t>522-03,149</t>
         </is>
       </c>
       <c r="F194" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G194" s="9" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="H194" s="10" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I194" s="11" t="n"/>
       <c r="J194" s="11" t="n"/>
     </row>
     <row r="195" ht="26" customHeight="1">
       <c r="A195" s="5" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15 Ру160</t>
+          <t>Клапан штуцерный угловой Ду10 Ру100</t>
         </is>
       </c>
       <c r="C195" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D195" s="5" t="n">
-        <v>160</v>
+        <v>10</v>
+      </c>
+      <c r="D195" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="E195" s="12" t="inlineStr">
         <is>
-          <t>521-03.387</t>
+          <t>521-01.465-01</t>
         </is>
       </c>
       <c r="F195" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G195" s="9" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="H195" s="10" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I195" s="11" t="n"/>
       <c r="J195" s="11" t="n"/>
     </row>
     <row r="196" ht="26" customHeight="1">
       <c r="A196" s="5" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15 Ру160</t>
+          <t>Клапан штуцерный угловой Ду10 Ру100</t>
         </is>
       </c>
       <c r="C196" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E196" s="12" t="inlineStr">
         <is>
-          <t>521-03.387</t>
+          <t>522-01.499-01</t>
         </is>
       </c>
       <c r="F196" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G196" s="9" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="H196" s="10" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I196" s="11" t="n"/>
       <c r="J196" s="11" t="n"/>
     </row>
     <row r="197" ht="26" customHeight="1">
       <c r="A197" s="5" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15Ру100</t>
+          <t>Клапан штуцерный угловой Ду10 Ру100</t>
         </is>
       </c>
       <c r="C197" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
@@ -6189,32 +6229,32 @@
       </c>
       <c r="E197" s="12" t="inlineStr">
         <is>
-          <t>522-01.500-04</t>
+          <t>521-01.467-03</t>
         </is>
       </c>
       <c r="F197" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G197" s="9" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="H197" s="10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I197" s="11" t="n"/>
       <c r="J197" s="11" t="n"/>
     </row>
     <row r="198" ht="26" customHeight="1">
       <c r="A198" s="5" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15Ру100</t>
+          <t>Клапан штуцерный угловой Ду10 Ру100</t>
         </is>
       </c>
       <c r="C198" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D198" s="5" t="inlineStr">
         <is>
@@ -6223,252 +6263,214 @@
       </c>
       <c r="E198" s="12" t="inlineStr">
         <is>
-          <t>521-01.464-01</t>
+          <t>521-01.493-02</t>
         </is>
       </c>
       <c r="F198" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G198" s="9" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="H198" s="10" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I198" s="11" t="n"/>
       <c r="J198" s="11" t="n"/>
     </row>
     <row r="199" ht="26" customHeight="1">
       <c r="A199" s="5" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15Ру100</t>
+          <t>Клапан предохранительный штуцерный угловой Ду6,5-9</t>
         </is>
       </c>
       <c r="C199" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D199" s="5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="D199" s="5" t="inlineStr"/>
       <c r="E199" s="12" t="inlineStr">
         <is>
-          <t>521-01.468</t>
+          <t>524-03.004</t>
         </is>
       </c>
       <c r="F199" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G199" s="9" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="H199" s="10" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="I199" s="11" t="n"/>
       <c r="J199" s="11" t="n"/>
     </row>
     <row r="200" ht="26" customHeight="1">
       <c r="A200" s="5" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15Ру40</t>
+          <t>Клапан штуцерный угловой Ду6Ру100</t>
         </is>
       </c>
       <c r="C200" s="5" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D200" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E200" s="12" t="inlineStr">
         <is>
-          <t>521-01.465-02</t>
+          <t>521-01.467-02</t>
         </is>
       </c>
       <c r="F200" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G200" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H200" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="G200" s="9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H200" s="10" t="n">
-        <v>5</v>
       </c>
       <c r="I200" s="11" t="n"/>
       <c r="J200" s="11" t="n"/>
     </row>
     <row r="201" ht="26" customHeight="1">
       <c r="A201" s="5" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду10 Р160</t>
-        </is>
-      </c>
-      <c r="C201" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D201" s="5" t="n">
-        <v>160</v>
-      </c>
+          <t>Клапан дроссельный угловой штуцерный</t>
+        </is>
+      </c>
+      <c r="C201" s="5" t="inlineStr"/>
+      <c r="D201" s="5" t="inlineStr"/>
       <c r="E201" s="12" t="inlineStr">
         <is>
-          <t>522-03.149</t>
+          <t>525-35.577</t>
         </is>
       </c>
       <c r="F201" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G201" s="9" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="H201" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I201" s="11" t="n"/>
       <c r="J201" s="11" t="n"/>
     </row>
     <row r="202" ht="26" customHeight="1">
       <c r="A202" s="5" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду10 Р160</t>
-        </is>
-      </c>
-      <c r="C202" s="5" t="n">
-        <v>10</v>
-      </c>
+          <t>Клапан штуцерный угловой Ду НЕРЖ</t>
+        </is>
+      </c>
+      <c r="C202" s="5" t="inlineStr"/>
       <c r="D202" s="5" t="inlineStr"/>
       <c r="E202" s="12" t="inlineStr">
         <is>
-          <t>522-03,149</t>
+          <t>521-03.472-01</t>
         </is>
       </c>
       <c r="F202" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G202" s="9" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="H202" s="10" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I202" s="11" t="n"/>
       <c r="J202" s="11" t="n"/>
     </row>
     <row r="203" ht="26" customHeight="1">
       <c r="A203" s="5" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду10 Ру100</t>
-        </is>
-      </c>
-      <c r="C203" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D203" s="5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+          <t>Клапан штуцерный угловой Рр150/10</t>
+        </is>
+      </c>
+      <c r="C203" s="5" t="inlineStr"/>
+      <c r="D203" s="5" t="n">
+        <v>150</v>
       </c>
       <c r="E203" s="12" t="inlineStr">
         <is>
-          <t>521-01.465-01</t>
+          <t>521-ц22п</t>
         </is>
       </c>
       <c r="F203" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G203" s="9" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="H203" s="10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I203" s="11" t="n"/>
       <c r="J203" s="11" t="n"/>
     </row>
     <row r="204" ht="26" customHeight="1">
       <c r="A204" s="5" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду10 Ру100</t>
-        </is>
-      </c>
-      <c r="C204" s="5" t="n">
+          <t>Клапан штуцерный угловой Рр150/10</t>
+        </is>
+      </c>
+      <c r="C204" s="5" t="inlineStr"/>
+      <c r="D204" s="5" t="inlineStr"/>
+      <c r="E204" s="12" t="inlineStr">
+        <is>
+          <t>521-ц22п</t>
+        </is>
+      </c>
+      <c r="F204" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G204" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H204" s="10" t="n">
         <v>10</v>
-      </c>
-      <c r="D204" s="5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E204" s="12" t="inlineStr">
-        <is>
-          <t>522-01.499-01</t>
-        </is>
-      </c>
-      <c r="F204" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G204" s="9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H204" s="10" t="n">
-        <v>2</v>
       </c>
       <c r="I204" s="11" t="n"/>
       <c r="J204" s="11" t="n"/>
     </row>
-    <row r="205" ht="26" customHeight="1">
-      <c r="A205" s="5" t="n">
-        <v>187</v>
-      </c>
-      <c r="B205" s="6" t="inlineStr">
-        <is>
-          <t>Клапан штуцерный угловой Ду10 Ру100</t>
-        </is>
-      </c>
-      <c r="C205" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D205" s="5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E205" s="12" t="inlineStr">
-        <is>
-          <t>521-01.467-03</t>
-        </is>
-      </c>
-      <c r="F205" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G205" s="9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H205" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="I205" s="11" t="n"/>
-      <c r="J205" s="11" t="n"/>
+    <row r="205" ht="22" customHeight="1">
+      <c r="A205" s="4" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная — 68 позиций  1 516 шт  2 449 кг</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="n"/>
+      <c r="C205" s="4" t="n"/>
+      <c r="D205" s="4" t="n"/>
+      <c r="E205" s="4" t="n"/>
+      <c r="F205" s="4" t="n"/>
+      <c r="G205" s="4" t="n"/>
+      <c r="H205" s="4" t="n"/>
+      <c r="I205" s="4" t="n"/>
+      <c r="J205" s="4" t="n"/>
     </row>
     <row r="206" ht="26" customHeight="1">
       <c r="A206" s="5" t="n">
@@ -6476,30 +6478,26 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду10 Ру100</t>
+          <t>Клапан муфтовый проходной запорный Ду32Ру10</t>
         </is>
       </c>
       <c r="C206" s="5" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E206" s="12" t="inlineStr">
-        <is>
-          <t>521-01.493-02</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E206" s="7" t="inlineStr"/>
       <c r="F206" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G206" s="9" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="H206" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I206" s="11" t="n"/>
       <c r="J206" s="11" t="n"/>
@@ -6510,26 +6508,30 @@
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный угловой Ду6,5-9</t>
+          <t>Клапан штуцерный проходной Ду 32 Ру 40</t>
         </is>
       </c>
       <c r="C207" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D207" s="5" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="D207" s="5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="E207" s="12" t="inlineStr">
         <is>
-          <t>524-03.004</t>
+          <t>521.3м.660</t>
         </is>
       </c>
       <c r="F207" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G207" s="9" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="H207" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I207" s="11" t="n"/>
       <c r="J207" s="11" t="n"/>
@@ -6540,30 +6542,30 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду6Ру100</t>
+          <t>Клапан муфтовый проходной запорный Ду25Ру16</t>
         </is>
       </c>
       <c r="C208" s="5" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E208" s="12" t="inlineStr">
         <is>
-          <t>521-01.467-02</t>
+          <t>521-03.124</t>
         </is>
       </c>
       <c r="F208" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G208" s="9" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="H208" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I208" s="11" t="n"/>
       <c r="J208" s="11" t="n"/>
@@ -6574,21 +6576,25 @@
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>Клапан дроссельный угловой штуцерный</t>
-        </is>
-      </c>
-      <c r="C209" s="5" t="inlineStr"/>
-      <c r="D209" s="5" t="inlineStr"/>
+          <t>Клапан муфтовый проходной запорный Ду25Ру16                             (Ду25Ру16 -1 шт ; Ду25Ру10 -1шт )</t>
+        </is>
+      </c>
+      <c r="C209" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="D209" s="5" t="n">
+        <v>16</v>
+      </c>
       <c r="E209" s="12" t="inlineStr">
         <is>
-          <t>525-35.577</t>
+          <t>521-03.124</t>
         </is>
       </c>
       <c r="F209" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G209" s="9" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="H209" s="10" t="n">
         <v>1</v>
@@ -6602,24 +6608,22 @@
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду НЕРЖ</t>
-        </is>
-      </c>
-      <c r="C210" s="5" t="inlineStr"/>
+          <t>Клапан штуцерный проходной Ду 25 (Китай)</t>
+        </is>
+      </c>
+      <c r="C210" s="5" t="n">
+        <v>25</v>
+      </c>
       <c r="D210" s="5" t="inlineStr"/>
-      <c r="E210" s="12" t="inlineStr">
-        <is>
-          <t>521-03.472-01</t>
-        </is>
-      </c>
+      <c r="E210" s="7" t="inlineStr"/>
       <c r="F210" s="8" t="n">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="G210" s="9" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="H210" s="10" t="n">
-        <v>1</v>
+        <v>138</v>
       </c>
       <c r="I210" s="11" t="n"/>
       <c r="J210" s="11" t="n"/>
@@ -6630,26 +6634,26 @@
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Рр150/10</t>
-        </is>
-      </c>
-      <c r="C211" s="5" t="inlineStr"/>
-      <c r="D211" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="E211" s="12" t="inlineStr">
-        <is>
-          <t>521-ц22п</t>
-        </is>
-      </c>
+          <t>Клапан муфтовый проходной запорный Ду20Ру16</t>
+        </is>
+      </c>
+      <c r="C211" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D211" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E211" s="7" t="inlineStr"/>
       <c r="F211" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G211" s="9" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="H211" s="10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I211" s="11" t="n"/>
       <c r="J211" s="11" t="n"/>
@@ -6660,207 +6664,227 @@
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Рр150/10</t>
-        </is>
-      </c>
-      <c r="C212" s="5" t="inlineStr"/>
-      <c r="D212" s="5" t="inlineStr"/>
+          <t>Клапан невозвратный штуцерный проходной Ду20 Ру40</t>
+        </is>
+      </c>
+      <c r="C212" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D212" s="5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="E212" s="12" t="inlineStr">
         <is>
-          <t>521-ц22п</t>
+          <t>522-3м-9</t>
         </is>
       </c>
       <c r="F212" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G212" s="9" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="H212" s="10" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I212" s="11" t="n"/>
       <c r="J212" s="11" t="n"/>
     </row>
-    <row r="213" ht="22" customHeight="1">
-      <c r="A213" s="4" t="inlineStr">
-        <is>
-          <t>Штуцерная проходная — 68 позиций  1 516 шт  2 449 кг</t>
-        </is>
-      </c>
-      <c r="B213" s="4" t="n"/>
-      <c r="C213" s="4" t="n"/>
-      <c r="D213" s="4" t="n"/>
-      <c r="E213" s="4" t="n"/>
-      <c r="F213" s="4" t="n"/>
-      <c r="G213" s="4" t="n"/>
-      <c r="H213" s="4" t="n"/>
-      <c r="I213" s="4" t="n"/>
-      <c r="J213" s="4" t="n"/>
+    <row r="213" ht="26" customHeight="1">
+      <c r="A213" s="5" t="n">
+        <v>195</v>
+      </c>
+      <c r="B213" s="6" t="inlineStr">
+        <is>
+          <t>Клапан невозвратный штуцерный проходной Ду20Ру160</t>
+        </is>
+      </c>
+      <c r="C213" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D213" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="E213" s="12" t="inlineStr">
+        <is>
+          <t>522-03.089</t>
+        </is>
+      </c>
+      <c r="F213" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" s="9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H213" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I213" s="11" t="n"/>
+      <c r="J213" s="11" t="n"/>
     </row>
     <row r="214" ht="26" customHeight="1">
       <c r="A214" s="5" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду32Ру10</t>
+          <t>Клапан невозвратный штуцерный проходной Ду20Ру160</t>
         </is>
       </c>
       <c r="C214" s="5" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E214" s="7" t="inlineStr"/>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="E214" s="12" t="inlineStr">
+        <is>
+          <t>522-03.089</t>
+        </is>
+      </c>
       <c r="F214" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G214" s="9" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="H214" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I214" s="11" t="n"/>
       <c r="J214" s="11" t="n"/>
     </row>
     <row r="215" ht="26" customHeight="1">
       <c r="A215" s="5" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B215" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 32 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 20</t>
         </is>
       </c>
       <c r="C215" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="D215" s="5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="E215" s="12" t="inlineStr">
-        <is>
-          <t>521.3м.660</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="D215" s="5" t="inlineStr"/>
+      <c r="E215" s="7" t="inlineStr"/>
       <c r="F215" s="8" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="G215" s="9" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="H215" s="10" t="n">
-        <v>10</v>
+        <v>195</v>
       </c>
       <c r="I215" s="11" t="n"/>
       <c r="J215" s="11" t="n"/>
     </row>
     <row r="216" ht="26" customHeight="1">
       <c r="A216" s="5" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду25Ру16</t>
+          <t>Клапан штуцерный проходной Ду 20</t>
         </is>
       </c>
       <c r="C216" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="D216" s="5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="D216" s="5" t="inlineStr"/>
       <c r="E216" s="12" t="inlineStr">
         <is>
-          <t>521-03.124</t>
+          <t>536-3м 5</t>
         </is>
       </c>
       <c r="F216" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G216" s="9" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="H216" s="10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I216" s="11" t="n"/>
       <c r="J216" s="11" t="n"/>
     </row>
     <row r="217" ht="26" customHeight="1">
       <c r="A217" s="5" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B217" s="6" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду25Ру16                             (Ду25Ру16 -1 шт ; Ду25Ру10 -1шт )</t>
+          <t>Клапан штуцерный проходной Ду 20</t>
         </is>
       </c>
       <c r="C217" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="D217" s="5" t="n">
-        <v>16</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="D217" s="5" t="inlineStr"/>
       <c r="E217" s="12" t="inlineStr">
         <is>
-          <t>521-03.124</t>
+          <t>536 3м .333</t>
         </is>
       </c>
       <c r="F217" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G217" s="9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H217" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="G217" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H217" s="10" t="n">
-        <v>1</v>
       </c>
       <c r="I217" s="11" t="n"/>
       <c r="J217" s="11" t="n"/>
     </row>
     <row r="218" ht="26" customHeight="1">
       <c r="A218" s="5" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 25 (Китай)</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
       <c r="C218" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="D218" s="5" t="inlineStr"/>
-      <c r="E218" s="7" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="D218" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E218" s="12" t="inlineStr">
+        <is>
+          <t>521-01.052</t>
+        </is>
+      </c>
       <c r="F218" s="8" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="G218" s="9" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="H218" s="10" t="n">
-        <v>138</v>
+        <v>2</v>
       </c>
       <c r="I218" s="11" t="n"/>
       <c r="J218" s="11" t="n"/>
     </row>
     <row r="219" ht="26" customHeight="1">
       <c r="A219" s="5" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B219" s="6" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду20Ру16</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
       <c r="C219" s="5" t="n">
@@ -6868,29 +6892,33 @@
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E219" s="7" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E219" s="12" t="inlineStr">
+        <is>
+          <t>521-01.470-02</t>
+        </is>
+      </c>
       <c r="F219" s="8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G219" s="9" t="n">
         <v>1.9</v>
       </c>
       <c r="H219" s="10" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I219" s="11" t="n"/>
       <c r="J219" s="11" t="n"/>
     </row>
     <row r="220" ht="26" customHeight="1">
       <c r="A220" s="5" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t>Клапан невозвратный штуцерный проходной Ду20 Ру40</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
       <c r="C220" s="5" t="n">
@@ -6898,12 +6926,12 @@
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E220" s="12" t="inlineStr">
         <is>
-          <t>522-3м-9</t>
+          <t>521-01.471-03</t>
         </is>
       </c>
       <c r="F220" s="8" t="n">
@@ -6920,43 +6948,45 @@
     </row>
     <row r="221" ht="26" customHeight="1">
       <c r="A221" s="5" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B221" s="6" t="inlineStr">
         <is>
-          <t>Клапан невозвратный штуцерный проходной Ду20Ру160</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
       <c r="C221" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D221" s="5" t="n">
-        <v>160</v>
+      <c r="D221" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="E221" s="12" t="inlineStr">
         <is>
-          <t>522-03.089</t>
+          <t>521-01.052</t>
         </is>
       </c>
       <c r="F221" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G221" s="9" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="H221" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I221" s="11" t="n"/>
       <c r="J221" s="11" t="n"/>
     </row>
     <row r="222" ht="26" customHeight="1">
       <c r="A222" s="5" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
-          <t>Клапан невозвратный штуцерный проходной Ду20Ру160</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
       <c r="C222" s="5" t="n">
@@ -6964,115 +6994,131 @@
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E222" s="12" t="inlineStr">
         <is>
-          <t>522-03.089</t>
+          <t>521-01.470-02</t>
         </is>
       </c>
       <c r="F222" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G222" s="9" t="n">
         <v>1.9</v>
       </c>
       <c r="H222" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I222" s="11" t="n"/>
       <c r="J222" s="11" t="n"/>
     </row>
     <row r="223" ht="26" customHeight="1">
       <c r="A223" s="5" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B223" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
       <c r="C223" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D223" s="5" t="inlineStr"/>
-      <c r="E223" s="7" t="inlineStr"/>
+      <c r="D223" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E223" s="12" t="inlineStr">
+        <is>
+          <t>521-01.498-03</t>
+        </is>
+      </c>
       <c r="F223" s="8" t="n">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="G223" s="9" t="n">
         <v>1.9</v>
       </c>
       <c r="H223" s="10" t="n">
-        <v>195</v>
+        <v>41</v>
       </c>
       <c r="I223" s="11" t="n"/>
       <c r="J223" s="11" t="n"/>
     </row>
     <row r="224" ht="26" customHeight="1">
       <c r="A224" s="5" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
       <c r="C224" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D224" s="5" t="inlineStr"/>
+      <c r="D224" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="E224" s="12" t="inlineStr">
         <is>
-          <t>536-3м 5</t>
+          <t>522-01.498-02</t>
         </is>
       </c>
       <c r="F224" s="8" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G224" s="9" t="n">
         <v>1.9</v>
       </c>
       <c r="H224" s="10" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="I224" s="11" t="n"/>
       <c r="J224" s="11" t="n"/>
     </row>
     <row r="225" ht="26" customHeight="1">
       <c r="A225" s="5" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B225" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
       <c r="C225" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D225" s="5" t="inlineStr"/>
+      <c r="D225" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="E225" s="12" t="inlineStr">
         <is>
-          <t>536 3м .333</t>
+          <t>521-01.468-05</t>
         </is>
       </c>
       <c r="F225" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G225" s="9" t="n">
         <v>1.9</v>
       </c>
       <c r="H225" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I225" s="11" t="n"/>
       <c r="J225" s="11" t="n"/>
     </row>
     <row r="226" ht="26" customHeight="1">
       <c r="A226" s="5" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
@@ -7089,7 +7135,7 @@
       </c>
       <c r="E226" s="12" t="inlineStr">
         <is>
-          <t>521-01.052</t>
+          <t>522-01.498.-03</t>
         </is>
       </c>
       <c r="F226" s="8" t="n">
@@ -7106,7 +7152,7 @@
     </row>
     <row r="227" ht="26" customHeight="1">
       <c r="A227" s="5" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B227" s="6" t="inlineStr">
         <is>
@@ -7123,24 +7169,24 @@
       </c>
       <c r="E227" s="12" t="inlineStr">
         <is>
-          <t>521-01.470-02</t>
+          <t>425-322710</t>
         </is>
       </c>
       <c r="F227" s="8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G227" s="9" t="n">
         <v>1.9</v>
       </c>
       <c r="H227" s="10" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I227" s="11" t="n"/>
       <c r="J227" s="11" t="n"/>
     </row>
     <row r="228" ht="26" customHeight="1">
       <c r="A228" s="5" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B228" s="6" t="inlineStr">
         <is>
@@ -7157,24 +7203,24 @@
       </c>
       <c r="E228" s="12" t="inlineStr">
         <is>
-          <t>521-01.471-03</t>
+          <t>521-01464-02</t>
         </is>
       </c>
       <c r="F228" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G228" s="9" t="n">
         <v>1.9</v>
       </c>
       <c r="H228" s="10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I228" s="11" t="n"/>
       <c r="J228" s="11" t="n"/>
     </row>
     <row r="229" ht="26" customHeight="1">
       <c r="A229" s="5" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B229" s="6" t="inlineStr">
         <is>
@@ -7191,24 +7237,24 @@
       </c>
       <c r="E229" s="12" t="inlineStr">
         <is>
-          <t>521-01.052</t>
+          <t>521-01.470-03</t>
         </is>
       </c>
       <c r="F229" s="8" t="n">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="G229" s="9" t="n">
         <v>1.9</v>
       </c>
       <c r="H229" s="10" t="n">
-        <v>4</v>
+        <v>199</v>
       </c>
       <c r="I229" s="11" t="n"/>
       <c r="J229" s="11" t="n"/>
     </row>
     <row r="230" ht="26" customHeight="1">
       <c r="A230" s="5" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B230" s="6" t="inlineStr">
         <is>
@@ -7225,24 +7271,24 @@
       </c>
       <c r="E230" s="12" t="inlineStr">
         <is>
-          <t>521-01.470-02</t>
+          <t>521-01464-03</t>
         </is>
       </c>
       <c r="F230" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G230" s="9" t="n">
         <v>1.9</v>
       </c>
       <c r="H230" s="10" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I230" s="11" t="n"/>
       <c r="J230" s="11" t="n"/>
     </row>
     <row r="231" ht="26" customHeight="1">
       <c r="A231" s="5" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B231" s="6" t="inlineStr">
         <is>
@@ -7259,28 +7305,28 @@
       </c>
       <c r="E231" s="12" t="inlineStr">
         <is>
-          <t>521-01.498-03</t>
+          <t>522-01500-05</t>
         </is>
       </c>
       <c r="F231" s="8" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G231" s="9" t="n">
         <v>1.9</v>
       </c>
       <c r="H231" s="10" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="I231" s="11" t="n"/>
       <c r="J231" s="11" t="n"/>
     </row>
     <row r="232" ht="26" customHeight="1">
       <c r="A232" s="5" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B232" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
       <c r="C232" s="5" t="n">
@@ -7288,33 +7334,33 @@
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E232" s="12" t="inlineStr">
         <is>
-          <t>522-01.498-02</t>
+          <t>Без чертежа</t>
         </is>
       </c>
       <c r="F232" s="8" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G232" s="9" t="n">
         <v>1.9</v>
       </c>
       <c r="H232" s="10" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="I232" s="11" t="n"/>
       <c r="J232" s="11" t="n"/>
     </row>
     <row r="233" ht="26" customHeight="1">
       <c r="A233" s="5" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B233" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
       <c r="C233" s="5" t="n">
@@ -7322,33 +7368,33 @@
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E233" s="12" t="inlineStr">
         <is>
-          <t>521-01.468-05</t>
+          <t>521-01474-03</t>
         </is>
       </c>
       <c r="F233" s="8" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G233" s="9" t="n">
         <v>1.9</v>
       </c>
       <c r="H233" s="10" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="I233" s="11" t="n"/>
       <c r="J233" s="11" t="n"/>
     </row>
     <row r="234" ht="26" customHeight="1">
       <c r="A234" s="5" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B234" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
       <c r="C234" s="5" t="n">
@@ -7356,33 +7402,33 @@
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E234" s="12" t="inlineStr">
         <is>
-          <t>522-01.498.-03</t>
+          <t>521 3м 623</t>
         </is>
       </c>
       <c r="F234" s="8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G234" s="9" t="n">
         <v>1.9</v>
       </c>
       <c r="H234" s="10" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="I234" s="11" t="n"/>
       <c r="J234" s="11" t="n"/>
     </row>
     <row r="235" ht="26" customHeight="1">
       <c r="A235" s="5" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B235" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
       <c r="C235" s="5" t="n">
@@ -7390,33 +7436,33 @@
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E235" s="12" t="inlineStr">
         <is>
-          <t>425-322710</t>
+          <t>521 3м 726</t>
         </is>
       </c>
       <c r="F235" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G235" s="9" t="n">
         <v>1.9</v>
       </c>
       <c r="H235" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I235" s="11" t="n"/>
       <c r="J235" s="11" t="n"/>
     </row>
     <row r="236" ht="26" customHeight="1">
       <c r="A236" s="5" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B236" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
       <c r="C236" s="5" t="n">
@@ -7424,33 +7470,33 @@
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E236" s="12" t="inlineStr">
         <is>
-          <t>521-01464-02</t>
+          <t>521 3м 30</t>
         </is>
       </c>
       <c r="F236" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G236" s="9" t="n">
         <v>1.9</v>
       </c>
       <c r="H236" s="10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I236" s="11" t="n"/>
       <c r="J236" s="11" t="n"/>
     </row>
     <row r="237" ht="26" customHeight="1">
       <c r="A237" s="5" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B237" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
       <c r="C237" s="5" t="n">
@@ -7458,33 +7504,33 @@
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E237" s="12" t="inlineStr">
         <is>
-          <t>521-01.470-03</t>
+          <t>522 3м 13</t>
         </is>
       </c>
       <c r="F237" s="8" t="n">
-        <v>102</v>
+        <v>3</v>
       </c>
       <c r="G237" s="9" t="n">
         <v>1.9</v>
       </c>
       <c r="H237" s="10" t="n">
-        <v>199</v>
+        <v>6</v>
       </c>
       <c r="I237" s="11" t="n"/>
       <c r="J237" s="11" t="n"/>
     </row>
     <row r="238" ht="26" customHeight="1">
       <c r="A238" s="5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B238" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
       <c r="C238" s="5" t="n">
@@ -7492,33 +7538,33 @@
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E238" s="12" t="inlineStr">
         <is>
-          <t>521-01464-03</t>
+          <t>522-01.501-02</t>
         </is>
       </c>
       <c r="F238" s="8" t="n">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="G238" s="9" t="n">
         <v>1.9</v>
       </c>
       <c r="H238" s="10" t="n">
-        <v>14</v>
+        <v>140</v>
       </c>
       <c r="I238" s="11" t="n"/>
       <c r="J238" s="11" t="n"/>
     </row>
     <row r="239" ht="26" customHeight="1">
       <c r="A239" s="5" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B239" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
       <c r="C239" s="5" t="n">
@@ -7526,33 +7572,33 @@
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E239" s="12" t="inlineStr">
         <is>
-          <t>522-01500-05</t>
+          <t>521 3м 58</t>
         </is>
       </c>
       <c r="F239" s="8" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="G239" s="9" t="n">
         <v>1.9</v>
       </c>
       <c r="H239" s="10" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="I239" s="11" t="n"/>
       <c r="J239" s="11" t="n"/>
     </row>
     <row r="240" ht="26" customHeight="1">
       <c r="A240" s="5" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B240" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 64</t>
         </is>
       </c>
       <c r="C240" s="5" t="n">
@@ -7560,33 +7606,33 @@
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E240" s="12" t="inlineStr">
         <is>
-          <t>Без чертежа</t>
+          <t>522-35 240</t>
         </is>
       </c>
       <c r="F240" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G240" s="9" t="n">
         <v>1.9</v>
       </c>
       <c r="H240" s="10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I240" s="11" t="n"/>
       <c r="J240" s="11" t="n"/>
     </row>
     <row r="241" ht="26" customHeight="1">
       <c r="A241" s="5" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B241" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру10</t>
         </is>
       </c>
       <c r="C241" s="5" t="n">
@@ -7594,337 +7640,329 @@
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E241" s="12" t="inlineStr">
         <is>
-          <t>521-01474-03</t>
+          <t>Без чертежа</t>
         </is>
       </c>
       <c r="F241" s="8" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G241" s="9" t="n">
         <v>1.9</v>
       </c>
       <c r="H241" s="10" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="I241" s="11" t="n"/>
       <c r="J241" s="11" t="n"/>
     </row>
     <row r="242" ht="26" customHeight="1">
       <c r="A242" s="5" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B242" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+          <t>(Кнопка)Клапан самозакрывающий проходной муфтовый Ду15Ру3</t>
         </is>
       </c>
       <c r="C242" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D242" s="5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="D242" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="E242" s="12" t="inlineStr">
         <is>
-          <t>521 3м 623</t>
+          <t>528-35.176</t>
         </is>
       </c>
       <c r="F242" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G242" s="9" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="H242" s="10" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I242" s="11" t="n"/>
       <c r="J242" s="11" t="n"/>
     </row>
     <row r="243" ht="26" customHeight="1">
       <c r="A243" s="5" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B243" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+          <t>(Кнопка)Клапан самозакрывающий проходной муфтовый Ду15Ру3</t>
         </is>
       </c>
       <c r="C243" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E243" s="12" t="inlineStr">
         <is>
-          <t>521 3м 726</t>
+          <t>528-35.176</t>
         </is>
       </c>
       <c r="F243" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G243" s="9" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="H243" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I243" s="11" t="n"/>
       <c r="J243" s="11" t="n"/>
     </row>
     <row r="244" ht="26" customHeight="1">
       <c r="A244" s="5" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B244" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 15</t>
         </is>
       </c>
       <c r="C244" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D244" s="5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="D244" s="5" t="inlineStr"/>
       <c r="E244" s="12" t="inlineStr">
         <is>
-          <t>521 3м 30</t>
+          <t>521 3м.770</t>
         </is>
       </c>
       <c r="F244" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G244" s="9" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="H244" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I244" s="11" t="n"/>
       <c r="J244" s="11" t="n"/>
     </row>
     <row r="245" ht="26" customHeight="1">
       <c r="A245" s="5" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B245" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 15</t>
         </is>
       </c>
       <c r="C245" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D245" s="5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="D245" s="5" t="inlineStr"/>
       <c r="E245" s="12" t="inlineStr">
         <is>
-          <t>522 3м 13</t>
+          <t>без чертежа</t>
         </is>
       </c>
       <c r="F245" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G245" s="9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H245" s="10" t="n">
         <v>3</v>
-      </c>
-      <c r="G245" s="9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H245" s="10" t="n">
-        <v>6</v>
       </c>
       <c r="I245" s="11" t="n"/>
       <c r="J245" s="11" t="n"/>
     </row>
     <row r="246" ht="26" customHeight="1">
       <c r="A246" s="5" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B246" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 15 Ру 100</t>
         </is>
       </c>
       <c r="C246" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E246" s="12" t="inlineStr">
         <is>
-          <t>522-01.501-02</t>
+          <t>522-01.498</t>
         </is>
       </c>
       <c r="F246" s="8" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="G246" s="9" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="H246" s="10" t="n">
-        <v>140</v>
+        <v>5</v>
       </c>
       <c r="I246" s="11" t="n"/>
       <c r="J246" s="11" t="n"/>
     </row>
     <row r="247" ht="26" customHeight="1">
       <c r="A247" s="5" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B247" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 15 Ру 100</t>
         </is>
       </c>
       <c r="C247" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E247" s="12" t="inlineStr">
         <is>
-          <t>521 3м 58</t>
+          <t>521-01.470</t>
         </is>
       </c>
       <c r="F247" s="8" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G247" s="9" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="H247" s="10" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="I247" s="11" t="n"/>
       <c r="J247" s="11" t="n"/>
     </row>
     <row r="248" ht="26" customHeight="1">
       <c r="A248" s="5" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B248" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 64</t>
+          <t>Клапан штуцерный проходной Ду 15 Ру 40</t>
         </is>
       </c>
       <c r="C248" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E248" s="12" t="inlineStr">
         <is>
-          <t>522-35 240</t>
+          <t>521. 3м.666</t>
         </is>
       </c>
       <c r="F248" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G248" s="9" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="H248" s="10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I248" s="11" t="n"/>
       <c r="J248" s="11" t="n"/>
     </row>
     <row r="249" ht="26" customHeight="1">
       <c r="A249" s="5" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B249" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру10</t>
+          <t>Клапан штуцерный проходной Ду 15 Ру 40</t>
         </is>
       </c>
       <c r="C249" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E249" s="12" t="inlineStr">
         <is>
-          <t>Без чертежа</t>
+          <t>521-01.470.02</t>
         </is>
       </c>
       <c r="F249" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G249" s="9" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="H249" s="10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I249" s="11" t="n"/>
       <c r="J249" s="11" t="n"/>
     </row>
     <row r="250" ht="26" customHeight="1">
       <c r="A250" s="5" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B250" s="6" t="inlineStr">
         <is>
-          <t>(Кнопка)Клапан самозакрывающий проходной муфтовый Ду15Ру3</t>
+          <t>Клапан штуцерный проходной Ду 15 Ру40</t>
         </is>
       </c>
       <c r="C250" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="D250" s="5" t="n">
+      <c r="D250" s="5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E250" s="12" t="inlineStr">
+        <is>
+          <t>522-01.501-01</t>
+        </is>
+      </c>
+      <c r="F250" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G250" s="9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H250" s="10" t="n">
         <v>3</v>
-      </c>
-      <c r="E250" s="12" t="inlineStr">
-        <is>
-          <t>528-35.176</t>
-        </is>
-      </c>
-      <c r="F250" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G250" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H250" s="10" t="n">
-        <v>1</v>
       </c>
       <c r="I250" s="11" t="n"/>
       <c r="J250" s="11" t="n"/>
     </row>
     <row r="251" ht="26" customHeight="1">
       <c r="A251" s="5" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B251" s="6" t="inlineStr">
         <is>
-          <t>(Кнопка)Клапан самозакрывающий проходной муфтовый Ду15Ру3</t>
+          <t>Клапан штуцерный проходной Ду 15 Ру40</t>
         </is>
       </c>
       <c r="C251" s="5" t="n">
@@ -7932,12 +7970,12 @@
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E251" s="12" t="inlineStr">
         <is>
-          <t>528-35.176</t>
+          <t>521-01.471-02</t>
         </is>
       </c>
       <c r="F251" s="8" t="n">
@@ -7954,11 +7992,11 @@
     </row>
     <row r="252" ht="26" customHeight="1">
       <c r="A252" s="5" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B252" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15</t>
+          <t>Клапан штуцерный проходной бессальниковый  Ду15/1</t>
         </is>
       </c>
       <c r="C252" s="5" t="n">
@@ -7967,28 +8005,28 @@
       <c r="D252" s="5" t="inlineStr"/>
       <c r="E252" s="12" t="inlineStr">
         <is>
-          <t>521 3м.770</t>
+          <t>521-35.2608-01</t>
         </is>
       </c>
       <c r="F252" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G252" s="9" t="n">
-        <v>2.6</v>
+        <v>5.7</v>
       </c>
       <c r="H252" s="10" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I252" s="11" t="n"/>
       <c r="J252" s="11" t="n"/>
     </row>
     <row r="253" ht="26" customHeight="1">
       <c r="A253" s="5" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B253" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15</t>
+          <t>Клапан штуцерный проходной бессальниковый Ду15/1</t>
         </is>
       </c>
       <c r="C253" s="5" t="n">
@@ -7997,168 +8035,150 @@
       <c r="D253" s="5" t="inlineStr"/>
       <c r="E253" s="12" t="inlineStr">
         <is>
-          <t>без чертежа</t>
+          <t>521-35.2608-01</t>
         </is>
       </c>
       <c r="F253" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G253" s="9" t="n">
         <v>2.6</v>
       </c>
       <c r="H253" s="10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I253" s="11" t="n"/>
       <c r="J253" s="11" t="n"/>
     </row>
     <row r="254" ht="26" customHeight="1">
       <c r="A254" s="5" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B254" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15 Ру 100</t>
+          <t>Клапан штущерный проходной Ду15</t>
         </is>
       </c>
       <c r="C254" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="D254" s="5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E254" s="12" t="inlineStr">
-        <is>
-          <t>522-01.498</t>
-        </is>
-      </c>
+      <c r="D254" s="5" t="inlineStr"/>
+      <c r="E254" s="7" t="inlineStr"/>
       <c r="F254" s="8" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="G254" s="9" t="n">
         <v>2.6</v>
       </c>
       <c r="H254" s="10" t="n">
-        <v>5</v>
+        <v>114</v>
       </c>
       <c r="I254" s="11" t="n"/>
       <c r="J254" s="11" t="n"/>
     </row>
     <row r="255" ht="26" customHeight="1">
       <c r="A255" s="5" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B255" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15 Ру 100</t>
+          <t>Клапан запорный штуцерный проходной Ду10 Ру16</t>
         </is>
       </c>
       <c r="C255" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D255" s="5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="D255" s="5" t="n">
+        <v>16</v>
       </c>
       <c r="E255" s="12" t="inlineStr">
         <is>
-          <t>521-01.470</t>
+          <t>521-35.2754</t>
         </is>
       </c>
       <c r="F255" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G255" s="9" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="H255" s="10" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I255" s="11" t="n"/>
       <c r="J255" s="11" t="n"/>
     </row>
     <row r="256" ht="26" customHeight="1">
       <c r="A256" s="5" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B256" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15 Ру 40</t>
+          <t>Клапан запорный штуцерный проходной Ду10 Ру16</t>
         </is>
       </c>
       <c r="C256" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E256" s="12" t="inlineStr">
         <is>
-          <t>521. 3м.666</t>
+          <t>521-35.2754</t>
         </is>
       </c>
       <c r="F256" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G256" s="9" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="H256" s="10" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I256" s="11" t="n"/>
       <c r="J256" s="11" t="n"/>
     </row>
     <row r="257" ht="26" customHeight="1">
       <c r="A257" s="5" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B257" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 10</t>
         </is>
       </c>
       <c r="C257" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D257" s="5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="E257" s="12" t="inlineStr">
-        <is>
-          <t>521-01.470.02</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D257" s="5" t="inlineStr"/>
+      <c r="E257" s="7" t="inlineStr"/>
       <c r="F257" s="8" t="n">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="G257" s="9" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="H257" s="10" t="n">
-        <v>3</v>
+        <v>193</v>
       </c>
       <c r="I257" s="11" t="n"/>
       <c r="J257" s="11" t="n"/>
     </row>
     <row r="258" ht="26" customHeight="1">
       <c r="A258" s="5" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B258" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15 Ру40</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру 40</t>
         </is>
       </c>
       <c r="C258" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
@@ -8167,32 +8187,32 @@
       </c>
       <c r="E258" s="12" t="inlineStr">
         <is>
-          <t>522-01.501-01</t>
+          <t>521-01.471-01</t>
         </is>
       </c>
       <c r="F258" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G258" s="9" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="H258" s="10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I258" s="11" t="n"/>
       <c r="J258" s="11" t="n"/>
     </row>
     <row r="259" ht="26" customHeight="1">
       <c r="A259" s="5" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B259" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15 Ру40</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру 40</t>
         </is>
       </c>
       <c r="C259" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
@@ -8201,146 +8221,164 @@
       </c>
       <c r="E259" s="12" t="inlineStr">
         <is>
-          <t>521-01.471-02</t>
+          <t>Без чертежа</t>
         </is>
       </c>
       <c r="F259" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G259" s="9" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="H259" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I259" s="11" t="n"/>
       <c r="J259" s="11" t="n"/>
     </row>
     <row r="260" ht="26" customHeight="1">
       <c r="A260" s="5" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B260" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной бессальниковый  Ду15/1</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
         </is>
       </c>
       <c r="C260" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D260" s="5" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="D260" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="E260" s="12" t="inlineStr">
         <is>
-          <t>521-35.2608-01</t>
+          <t>521-01.469-03</t>
         </is>
       </c>
       <c r="F260" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G260" s="9" t="n">
-        <v>5.7</v>
+        <v>2.3</v>
       </c>
       <c r="H260" s="10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I260" s="11" t="n"/>
       <c r="J260" s="11" t="n"/>
     </row>
     <row r="261" ht="26" customHeight="1">
       <c r="A261" s="5" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B261" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной бессальниковый Ду15/1</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
         </is>
       </c>
       <c r="C261" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D261" s="5" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="D261" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="E261" s="12" t="inlineStr">
         <is>
-          <t>521-35.2608-01</t>
+          <t>521-01.469-02</t>
         </is>
       </c>
       <c r="F261" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G261" s="9" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="H261" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I261" s="11" t="n"/>
       <c r="J261" s="11" t="n"/>
     </row>
     <row r="262" ht="26" customHeight="1">
       <c r="A262" s="5" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B262" s="6" t="inlineStr">
         <is>
-          <t>Клапан штущерный проходной Ду15</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
         </is>
       </c>
       <c r="C262" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D262" s="5" t="inlineStr"/>
-      <c r="E262" s="7" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="D262" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E262" s="12" t="inlineStr">
+        <is>
+          <t>522-01.497</t>
+        </is>
+      </c>
       <c r="F262" s="8" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="G262" s="9" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="H262" s="10" t="n">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="I262" s="11" t="n"/>
       <c r="J262" s="11" t="n"/>
     </row>
     <row r="263" ht="26" customHeight="1">
       <c r="A263" s="5" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B263" s="6" t="inlineStr">
         <is>
-          <t>Клапан запорный штуцерный проходной Ду10 Ру16</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
         </is>
       </c>
       <c r="C263" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D263" s="5" t="n">
-        <v>16</v>
+      <c r="D263" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="E263" s="12" t="inlineStr">
         <is>
-          <t>521-35.2754</t>
+          <t>521-01.469-02</t>
         </is>
       </c>
       <c r="F263" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G263" s="9" t="n">
         <v>2.3</v>
       </c>
       <c r="H263" s="10" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I263" s="11" t="n"/>
       <c r="J263" s="11" t="n"/>
     </row>
     <row r="264" ht="26" customHeight="1">
       <c r="A264" s="5" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B264" s="6" t="inlineStr">
         <is>
-          <t>Клапан запорный штуцерный проходной Ду10 Ру16</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру25 СТАЛЬ</t>
         </is>
       </c>
       <c r="C264" s="5" t="n">
@@ -8348,59 +8386,65 @@
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E264" s="12" t="inlineStr">
         <is>
-          <t>521-35.2754</t>
+          <t>521-3м-953</t>
         </is>
       </c>
       <c r="F264" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G264" s="9" t="n">
         <v>2.3</v>
       </c>
       <c r="H264" s="10" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I264" s="11" t="n"/>
       <c r="J264" s="11" t="n"/>
     </row>
     <row r="265" ht="26" customHeight="1">
       <c r="A265" s="5" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B265" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру40</t>
         </is>
       </c>
       <c r="C265" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D265" s="5" t="inlineStr"/>
-      <c r="E265" s="7" t="inlineStr"/>
+      <c r="D265" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="E265" s="12" t="inlineStr">
+        <is>
+          <t>521-01.471-01</t>
+        </is>
+      </c>
       <c r="F265" s="8" t="n">
-        <v>83</v>
+        <v>798</v>
       </c>
       <c r="G265" s="9" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="H265" s="10" t="n">
-        <v>193</v>
+        <v>958</v>
       </c>
       <c r="I265" s="11" t="n"/>
       <c r="J265" s="11" t="n"/>
     </row>
     <row r="266" ht="26" customHeight="1">
       <c r="A266" s="5" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B266" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру40</t>
         </is>
       </c>
       <c r="C266" s="5" t="n">
@@ -8417,58 +8461,56 @@
         </is>
       </c>
       <c r="F266" s="8" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G266" s="9" t="n">
         <v>2.3</v>
       </c>
       <c r="H266" s="10" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="I266" s="11" t="n"/>
       <c r="J266" s="11" t="n"/>
     </row>
     <row r="267" ht="26" customHeight="1">
       <c r="A267" s="5" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B267" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру400</t>
         </is>
       </c>
       <c r="C267" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D267" s="5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="D267" s="5" t="n">
+        <v>400</v>
       </c>
       <c r="E267" s="12" t="inlineStr">
         <is>
-          <t>Без чертежа</t>
+          <t>521-35.3238</t>
         </is>
       </c>
       <c r="F267" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G267" s="9" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="H267" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I267" s="11" t="n"/>
       <c r="J267" s="11" t="n"/>
     </row>
     <row r="268" ht="26" customHeight="1">
       <c r="A268" s="5" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B268" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру400</t>
         </is>
       </c>
       <c r="C268" s="5" t="n">
@@ -8476,33 +8518,33 @@
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E268" s="12" t="inlineStr">
         <is>
-          <t>521-01.469-03</t>
+          <t>521-35.3238</t>
         </is>
       </c>
       <c r="F268" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G268" s="9" t="n">
         <v>2.3</v>
       </c>
       <c r="H268" s="10" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I268" s="11" t="n"/>
       <c r="J268" s="11" t="n"/>
     </row>
     <row r="269" ht="26" customHeight="1">
       <c r="A269" s="5" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B269" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру400</t>
         </is>
       </c>
       <c r="C269" s="5" t="n">
@@ -8510,12 +8552,12 @@
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E269" s="12" t="inlineStr">
         <is>
-          <t>521-01.469-02</t>
+          <t>521-03.420</t>
         </is>
       </c>
       <c r="F269" s="8" t="n">
@@ -8532,11 +8574,11 @@
     </row>
     <row r="270" ht="26" customHeight="1">
       <c r="A270" s="5" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B270" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру6</t>
         </is>
       </c>
       <c r="C270" s="5" t="n">
@@ -8544,33 +8586,33 @@
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E270" s="12" t="inlineStr">
         <is>
-          <t>522-01.497</t>
+          <t>521-3м-52</t>
         </is>
       </c>
       <c r="F270" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G270" s="9" t="n">
         <v>2.3</v>
       </c>
       <c r="H270" s="10" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I270" s="11" t="n"/>
       <c r="J270" s="11" t="n"/>
     </row>
     <row r="271" ht="26" customHeight="1">
       <c r="A271" s="5" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B271" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру63 СТАЛЬ</t>
         </is>
       </c>
       <c r="C271" s="5" t="n">
@@ -8578,12 +8620,12 @@
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>63</t>
         </is>
       </c>
       <c r="E271" s="12" t="inlineStr">
         <is>
-          <t>521-01.469-02</t>
+          <t>522-03.134</t>
         </is>
       </c>
       <c r="F271" s="8" t="n">
@@ -8600,11 +8642,11 @@
     </row>
     <row r="272" ht="26" customHeight="1">
       <c r="A272" s="5" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B272" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру25 СТАЛЬ</t>
+          <t>Клапан штуцерный проходной невозвратный Ду10Ру100</t>
         </is>
       </c>
       <c r="C272" s="5" t="n">
@@ -8612,91 +8654,75 @@
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E272" s="12" t="inlineStr">
         <is>
-          <t>521-3м-953</t>
+          <t>522-01-493</t>
         </is>
       </c>
       <c r="F272" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G272" s="9" t="n">
         <v>2.3</v>
       </c>
       <c r="H272" s="10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I272" s="11" t="n"/>
       <c r="J272" s="11" t="n"/>
     </row>
     <row r="273" ht="26" customHeight="1">
       <c r="A273" s="5" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B273" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру40</t>
+          <t>Клапан штуцерный проходной невозвратный Ду10Ру100</t>
         </is>
       </c>
       <c r="C273" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D273" s="5" t="n">
-        <v>40</v>
+      <c r="D273" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="E273" s="12" t="inlineStr">
         <is>
-          <t>521-01.471-01</t>
+          <t>522-01-493-01</t>
         </is>
       </c>
       <c r="F273" s="8" t="n">
-        <v>798</v>
+        <v>1</v>
       </c>
       <c r="G273" s="9" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="H273" s="10" t="n">
-        <v>958</v>
+        <v>2</v>
       </c>
       <c r="I273" s="11" t="n"/>
       <c r="J273" s="11" t="n"/>
     </row>
-    <row r="274" ht="26" customHeight="1">
-      <c r="A274" s="5" t="n">
-        <v>255</v>
-      </c>
-      <c r="B274" s="6" t="inlineStr">
-        <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру40</t>
-        </is>
-      </c>
-      <c r="C274" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D274" s="5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="E274" s="12" t="inlineStr">
-        <is>
-          <t>521-01.471-01</t>
-        </is>
-      </c>
-      <c r="F274" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="G274" s="9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H274" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="I274" s="11" t="n"/>
-      <c r="J274" s="11" t="n"/>
+    <row r="274" ht="22" customHeight="1">
+      <c r="A274" s="4" t="inlineStr">
+        <is>
+          <t>Краны — 7 позиций  54 шт  112 кг</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="n"/>
+      <c r="C274" s="4" t="n"/>
+      <c r="D274" s="4" t="n"/>
+      <c r="E274" s="4" t="n"/>
+      <c r="F274" s="4" t="n"/>
+      <c r="G274" s="4" t="n"/>
+      <c r="H274" s="4" t="n"/>
+      <c r="I274" s="4" t="n"/>
+      <c r="J274" s="4" t="n"/>
     </row>
     <row r="275" ht="26" customHeight="1">
       <c r="A275" s="5" t="n">
@@ -8704,28 +8730,28 @@
       </c>
       <c r="B275" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру400</t>
+          <t>Кран двухходовой фланцевый Ду32 Ру6</t>
         </is>
       </c>
       <c r="C275" s="5" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D275" s="5" t="n">
-        <v>400</v>
+        <v>6</v>
       </c>
       <c r="E275" s="12" t="inlineStr">
         <is>
-          <t>521-35.3238</t>
+          <t>536-3М.72</t>
         </is>
       </c>
       <c r="F275" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G275" s="9" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="H275" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I275" s="11" t="n"/>
       <c r="J275" s="11" t="n"/>
@@ -8736,30 +8762,28 @@
       </c>
       <c r="B276" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру400</t>
+          <t>Кран трехходовой штуцерный Ду32 Ру10</t>
         </is>
       </c>
       <c r="C276" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="D276" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D276" s="5" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
       <c r="E276" s="12" t="inlineStr">
         <is>
-          <t>521-35.3238</t>
+          <t>536-35.696</t>
         </is>
       </c>
       <c r="F276" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G276" s="9" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="H276" s="10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I276" s="11" t="n"/>
       <c r="J276" s="11" t="n"/>
@@ -8770,30 +8794,28 @@
       </c>
       <c r="B277" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру400</t>
+          <t>Кран трехходовой штуцерный Ду32 Ру10</t>
         </is>
       </c>
       <c r="C277" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="D277" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D277" s="5" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
       <c r="E277" s="12" t="inlineStr">
         <is>
-          <t>521-03.420</t>
+          <t>536-35.696</t>
         </is>
       </c>
       <c r="F277" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G277" s="9" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="H277" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I277" s="11" t="n"/>
       <c r="J277" s="11" t="n"/>
@@ -8804,30 +8826,28 @@
       </c>
       <c r="B278" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру6</t>
+          <t>Кран двухходовой штуцерный Ду20 Ру16</t>
         </is>
       </c>
       <c r="C278" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D278" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="D278" s="5" t="n">
+        <v>16</v>
       </c>
       <c r="E278" s="12" t="inlineStr">
         <is>
-          <t>521-3м-52</t>
+          <t>536-3М5</t>
         </is>
       </c>
       <c r="F278" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G278" s="9" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="H278" s="10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I278" s="11" t="n"/>
       <c r="J278" s="11" t="n"/>
@@ -8838,30 +8858,28 @@
       </c>
       <c r="B279" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру63 СТАЛЬ</t>
+          <t>Кран трехходовой штуцерный Ду20 Ру16</t>
         </is>
       </c>
       <c r="C279" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D279" s="5" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="D279" s="5" t="n">
+        <v>16</v>
       </c>
       <c r="E279" s="12" t="inlineStr">
         <is>
-          <t>522-03.134</t>
+          <t>536-35.695</t>
         </is>
       </c>
       <c r="F279" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G279" s="9" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="H279" s="10" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="I279" s="11" t="n"/>
       <c r="J279" s="11" t="n"/>
@@ -8872,30 +8890,30 @@
       </c>
       <c r="B280" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной невозвратный Ду10Ру100</t>
+          <t>Кран штуцерный спусковой самозапорный проходной Ду20 Ру10</t>
         </is>
       </c>
       <c r="C280" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E280" s="12" t="inlineStr">
         <is>
-          <t>522-01-493</t>
+          <t>528-3М129</t>
         </is>
       </c>
       <c r="F280" s="8" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="G280" s="9" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="H280" s="10" t="n">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="I280" s="11" t="n"/>
       <c r="J280" s="11" t="n"/>
@@ -8906,30 +8924,26 @@
       </c>
       <c r="B281" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной невозвратный Ду10Ру100</t>
+          <t>Кран штуцерный спусковой самозапорный проходной Ду15 Ру25</t>
         </is>
       </c>
       <c r="C281" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E281" s="12" t="inlineStr">
-        <is>
-          <t>522-01-493-01</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E281" s="7" t="inlineStr"/>
       <c r="F281" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G281" s="9" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="H281" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I281" s="11" t="n"/>
       <c r="J281" s="11" t="n"/>
@@ -8937,7 +8951,7 @@
     <row r="282" ht="22" customHeight="1">
       <c r="A282" s="4" t="inlineStr">
         <is>
-          <t>Краны — 7 позиций  54 шт  112 кг</t>
+          <t>Пусковые клапаны — 2 позиции  15 шт  110 кг</t>
         </is>
       </c>
       <c r="B282" s="4" t="n"/>
@@ -8956,28 +8970,28 @@
       </c>
       <c r="B283" s="6" t="inlineStr">
         <is>
-          <t>Кран двухходовой фланцевый Ду32 Ру6</t>
+          <t>Клапан пусковой Ду32Ру125</t>
         </is>
       </c>
       <c r="C283" s="5" t="n">
         <v>32</v>
       </c>
       <c r="D283" s="5" t="n">
-        <v>6</v>
+        <v>125</v>
       </c>
       <c r="E283" s="12" t="inlineStr">
         <is>
-          <t>536-3М.72</t>
+          <t>587-03.082</t>
         </is>
       </c>
       <c r="F283" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G283" s="9" t="n">
-        <v>5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H283" s="10" t="n">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="I283" s="11" t="n"/>
       <c r="J283" s="11" t="n"/>
@@ -8988,268 +9002,248 @@
       </c>
       <c r="B284" s="6" t="inlineStr">
         <is>
-          <t>Кран трехходовой штуцерный Ду32 Ру10</t>
+          <t>Клапан пусковой Ду20Ру125</t>
         </is>
       </c>
       <c r="C284" s="5" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D284" s="5" t="n">
-        <v>10</v>
+        <v>125</v>
       </c>
       <c r="E284" s="12" t="inlineStr">
         <is>
-          <t>536-35.696</t>
+          <t>587-03.080</t>
         </is>
       </c>
       <c r="F284" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G284" s="9" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="H284" s="10" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="I284" s="11" t="n"/>
       <c r="J284" s="11" t="n"/>
     </row>
-    <row r="285" ht="26" customHeight="1">
-      <c r="A285" s="5" t="n">
-        <v>265</v>
-      </c>
-      <c r="B285" s="6" t="inlineStr">
-        <is>
-          <t>Кран трехходовой штуцерный Ду32 Ру10</t>
-        </is>
-      </c>
-      <c r="C285" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="D285" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E285" s="12" t="inlineStr">
-        <is>
-          <t>536-35.696</t>
-        </is>
-      </c>
-      <c r="F285" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G285" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H285" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="I285" s="11" t="n"/>
-      <c r="J285" s="11" t="n"/>
+    <row r="285" ht="22" customHeight="1">
+      <c r="A285" s="4" t="inlineStr">
+        <is>
+          <t>Педальные клапаны — 2 позиции  63 шт  346 кг</t>
+        </is>
+      </c>
+      <c r="B285" s="4" t="n"/>
+      <c r="C285" s="4" t="n"/>
+      <c r="D285" s="4" t="n"/>
+      <c r="E285" s="4" t="n"/>
+      <c r="F285" s="4" t="n"/>
+      <c r="G285" s="4" t="n"/>
+      <c r="H285" s="4" t="n"/>
+      <c r="I285" s="4" t="n"/>
+      <c r="J285" s="4" t="n"/>
     </row>
     <row r="286" ht="26" customHeight="1">
       <c r="A286" s="5" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B286" s="6" t="inlineStr">
         <is>
-          <t>Кран двухходовой штуцерный Ду20 Ру16</t>
+          <t>Клапан педальный Ду25</t>
         </is>
       </c>
       <c r="C286" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D286" s="5" t="n">
-        <v>16</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="D286" s="5" t="inlineStr"/>
       <c r="E286" s="12" t="inlineStr">
         <is>
-          <t>536-3М5</t>
+          <t>М528-03.001</t>
         </is>
       </c>
       <c r="F286" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G286" s="9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H286" s="10" t="n">
         <v>6</v>
-      </c>
-      <c r="G286" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H286" s="10" t="n">
-        <v>7</v>
       </c>
       <c r="I286" s="11" t="n"/>
       <c r="J286" s="11" t="n"/>
     </row>
     <row r="287" ht="26" customHeight="1">
       <c r="A287" s="5" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B287" s="6" t="inlineStr">
         <is>
-          <t>Кран трехходовой штуцерный Ду20 Ру16</t>
+          <t>Клапан педальный Ду25 новый приход</t>
         </is>
       </c>
       <c r="C287" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D287" s="5" t="n">
-        <v>16</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="D287" s="5" t="inlineStr"/>
       <c r="E287" s="12" t="inlineStr">
         <is>
-          <t>536-35.695</t>
+          <t>М528-03.001</t>
         </is>
       </c>
       <c r="F287" s="8" t="n">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="G287" s="9" t="n">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
       <c r="H287" s="10" t="n">
-        <v>20</v>
+        <v>341</v>
       </c>
       <c r="I287" s="11" t="n"/>
       <c r="J287" s="11" t="n"/>
     </row>
-    <row r="288" ht="26" customHeight="1">
-      <c r="A288" s="5" t="n">
-        <v>268</v>
-      </c>
-      <c r="B288" s="6" t="inlineStr">
-        <is>
-          <t>Кран штуцерный спусковой самозапорный проходной Ду20 Ру10</t>
-        </is>
-      </c>
-      <c r="C288" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D288" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E288" s="12" t="inlineStr">
-        <is>
-          <t>528-3М129</t>
-        </is>
-      </c>
-      <c r="F288" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="G288" s="9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H288" s="10" t="n">
-        <v>64</v>
-      </c>
-      <c r="I288" s="11" t="n"/>
-      <c r="J288" s="11" t="n"/>
+    <row r="288" ht="22" customHeight="1">
+      <c r="A288" s="4" t="inlineStr">
+        <is>
+          <t>Стаканы переборочные — 4 позиции  36 шт  52 кг</t>
+        </is>
+      </c>
+      <c r="B288" s="4" t="n"/>
+      <c r="C288" s="4" t="n"/>
+      <c r="D288" s="4" t="n"/>
+      <c r="E288" s="4" t="n"/>
+      <c r="F288" s="4" t="n"/>
+      <c r="G288" s="4" t="n"/>
+      <c r="H288" s="4" t="n"/>
+      <c r="I288" s="4" t="n"/>
+      <c r="J288" s="4" t="n"/>
     </row>
     <row r="289" ht="26" customHeight="1">
       <c r="A289" s="5" t="n">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B289" s="6" t="inlineStr">
         <is>
-          <t>Кран штуцерный спусковой самозапорный проходной Ду15 Ру25</t>
+          <t>Стакан переборочный Ду25Ру100</t>
         </is>
       </c>
       <c r="C289" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D289" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E289" s="7" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="D289" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E289" s="12" t="inlineStr">
+        <is>
+          <t>554-35.156</t>
+        </is>
+      </c>
       <c r="F289" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G289" s="9" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="H289" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I289" s="11" t="n"/>
       <c r="J289" s="11" t="n"/>
     </row>
-    <row r="290" ht="22" customHeight="1">
-      <c r="A290" s="4" t="inlineStr">
-        <is>
-          <t>Пусковые клапаны — 2 позиции  15 шт  110 кг</t>
-        </is>
-      </c>
-      <c r="B290" s="4" t="n"/>
-      <c r="C290" s="4" t="n"/>
-      <c r="D290" s="4" t="n"/>
-      <c r="E290" s="4" t="n"/>
-      <c r="F290" s="4" t="n"/>
-      <c r="G290" s="4" t="n"/>
-      <c r="H290" s="4" t="n"/>
-      <c r="I290" s="4" t="n"/>
-      <c r="J290" s="4" t="n"/>
+    <row r="290" ht="26" customHeight="1">
+      <c r="A290" s="5" t="n">
+        <v>268</v>
+      </c>
+      <c r="B290" s="6" t="inlineStr">
+        <is>
+          <t>Стакан переборочный Ду20Ру100</t>
+        </is>
+      </c>
+      <c r="C290" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D290" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E290" s="12" t="inlineStr">
+        <is>
+          <t>554-03.909-03</t>
+        </is>
+      </c>
+      <c r="F290" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G290" s="9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H290" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I290" s="11" t="n"/>
+      <c r="J290" s="11" t="n"/>
     </row>
     <row r="291" ht="26" customHeight="1">
       <c r="A291" s="5" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B291" s="6" t="inlineStr">
         <is>
-          <t>Клапан пусковой Ду32Ру125</t>
+          <t>Стакан переборочный Ду20Ру100</t>
         </is>
       </c>
       <c r="C291" s="5" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D291" s="5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="E291" s="12" t="inlineStr">
         <is>
-          <t>587-03.082</t>
+          <t>554-03.905-06</t>
         </is>
       </c>
       <c r="F291" s="8" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="G291" s="9" t="n">
-        <v>8.800000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="H291" s="10" t="n">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="I291" s="11" t="n"/>
       <c r="J291" s="11" t="n"/>
     </row>
     <row r="292" ht="26" customHeight="1">
       <c r="A292" s="5" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B292" s="6" t="inlineStr">
         <is>
-          <t>Клапан пусковой Ду20Ру125</t>
+          <t>Стакан переборочный Ду10Ру100</t>
         </is>
       </c>
       <c r="C292" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D292" s="5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="E292" s="12" t="inlineStr">
         <is>
-          <t>587-03.080</t>
+          <t>554-35.265</t>
         </is>
       </c>
       <c r="F292" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G292" s="9" t="n">
-        <v>5.6</v>
+        <v>0.6</v>
       </c>
       <c r="H292" s="10" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="I292" s="11" t="n"/>
       <c r="J292" s="11" t="n"/>
@@ -9257,7 +9251,7 @@
     <row r="293" ht="22" customHeight="1">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>Педальные клапаны — 2 позиции  63 шт  346 кг</t>
+          <t>Редукционные клапаны — 3 позиции  11 шт  258 кг</t>
         </is>
       </c>
       <c r="B293" s="4" t="n"/>
@@ -9272,505 +9266,505 @@
     </row>
     <row r="294" ht="26" customHeight="1">
       <c r="A294" s="5" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B294" s="6" t="inlineStr">
         <is>
-          <t>Клапан педальный Ду25</t>
+          <t>Клапан редукционный штуц.проход.односедельный Ду20Ру400 у входа</t>
         </is>
       </c>
       <c r="C294" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="D294" s="5" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="D294" s="5" t="n">
+        <v>400</v>
+      </c>
       <c r="E294" s="12" t="inlineStr">
         <is>
-          <t>М528-03.001</t>
+          <t>525-03.044</t>
         </is>
       </c>
       <c r="F294" s="8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G294" s="9" t="n">
-        <v>5.5</v>
+        <v>27</v>
       </c>
       <c r="H294" s="10" t="n">
-        <v>6</v>
+        <v>243</v>
       </c>
       <c r="I294" s="11" t="n"/>
       <c r="J294" s="11" t="n"/>
     </row>
     <row r="295" ht="26" customHeight="1">
       <c r="A295" s="5" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B295" s="6" t="inlineStr">
         <is>
-          <t>Клапан педальный Ду25 новый приход</t>
+          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
         </is>
       </c>
       <c r="C295" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="D295" s="5" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="D295" s="5" t="n">
+        <v>200</v>
+      </c>
       <c r="E295" s="12" t="inlineStr">
         <is>
-          <t>М528-03.001</t>
+          <t>525-35.2634</t>
         </is>
       </c>
       <c r="F295" s="8" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="G295" s="9" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="H295" s="10" t="n">
-        <v>341</v>
+        <v>8</v>
       </c>
       <c r="I295" s="11" t="n"/>
       <c r="J295" s="11" t="n"/>
     </row>
-    <row r="296" ht="22" customHeight="1">
-      <c r="A296" s="4" t="inlineStr">
-        <is>
-          <t>Стаканы переборочные — 4 позиции  36 шт  52 кг</t>
-        </is>
-      </c>
-      <c r="B296" s="4" t="n"/>
-      <c r="C296" s="4" t="n"/>
-      <c r="D296" s="4" t="n"/>
-      <c r="E296" s="4" t="n"/>
-      <c r="F296" s="4" t="n"/>
-      <c r="G296" s="4" t="n"/>
-      <c r="H296" s="4" t="n"/>
-      <c r="I296" s="4" t="n"/>
-      <c r="J296" s="4" t="n"/>
-    </row>
-    <row r="297" ht="26" customHeight="1">
-      <c r="A297" s="5" t="n">
-        <v>274</v>
-      </c>
-      <c r="B297" s="6" t="inlineStr">
-        <is>
-          <t>Стакан переборочный Ду25Ру100</t>
-        </is>
-      </c>
-      <c r="C297" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="D297" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E297" s="12" t="inlineStr">
-        <is>
-          <t>554-35.156</t>
-        </is>
-      </c>
-      <c r="F297" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G297" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H297" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="I297" s="11" t="n"/>
-      <c r="J297" s="11" t="n"/>
+    <row r="296" ht="26" customHeight="1">
+      <c r="A296" s="5" t="n">
+        <v>273</v>
+      </c>
+      <c r="B296" s="6" t="inlineStr">
+        <is>
+          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
+        </is>
+      </c>
+      <c r="C296" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D296" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E296" s="12" t="inlineStr">
+        <is>
+          <t>525-35.2634-04</t>
+        </is>
+      </c>
+      <c r="F296" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G296" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H296" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I296" s="11" t="n"/>
+      <c r="J296" s="11" t="n"/>
+    </row>
+    <row r="297" ht="22" customHeight="1">
+      <c r="A297" s="4" t="inlineStr">
+        <is>
+          <t>Электромагнитные клапаны — 4 позиции  7 шт  85 кг</t>
+        </is>
+      </c>
+      <c r="B297" s="4" t="n"/>
+      <c r="C297" s="4" t="n"/>
+      <c r="D297" s="4" t="n"/>
+      <c r="E297" s="4" t="n"/>
+      <c r="F297" s="4" t="n"/>
+      <c r="G297" s="4" t="n"/>
+      <c r="H297" s="4" t="n"/>
+      <c r="I297" s="4" t="n"/>
+      <c r="J297" s="4" t="n"/>
     </row>
     <row r="298" ht="26" customHeight="1">
       <c r="A298" s="5" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B298" s="6" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду20Ру100</t>
+          <t>Клапан с электромагнитным ручным управлением Ду20/10 перем. 220В</t>
         </is>
       </c>
       <c r="C298" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D298" s="5" t="n">
-        <v>100</v>
-      </c>
+      <c r="D298" s="5" t="inlineStr"/>
       <c r="E298" s="12" t="inlineStr">
         <is>
-          <t>554-03.909-03</t>
+          <t>587-35.8490-04</t>
         </is>
       </c>
       <c r="F298" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G298" s="9" t="n">
-        <v>1.7</v>
+        <v>11.6</v>
       </c>
       <c r="H298" s="10" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I298" s="11" t="n"/>
       <c r="J298" s="11" t="n"/>
     </row>
     <row r="299" ht="26" customHeight="1">
       <c r="A299" s="5" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B299" s="6" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду20Ру100</t>
-        </is>
-      </c>
-      <c r="C299" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D299" s="5" t="n">
-        <v>100</v>
-      </c>
+          <t>Клапан с электромагнитным ручным управлением</t>
+        </is>
+      </c>
+      <c r="C299" s="5" t="inlineStr"/>
+      <c r="D299" s="5" t="inlineStr"/>
       <c r="E299" s="12" t="inlineStr">
         <is>
-          <t>554-03.905-06</t>
+          <t>587-182.126</t>
         </is>
       </c>
       <c r="F299" s="8" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="G299" s="9" t="n">
-        <v>1.5</v>
+        <v>12.3</v>
       </c>
       <c r="H299" s="10" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="I299" s="11" t="n"/>
       <c r="J299" s="11" t="n"/>
     </row>
     <row r="300" ht="26" customHeight="1">
       <c r="A300" s="5" t="n">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B300" s="6" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду10Ру100</t>
-        </is>
-      </c>
-      <c r="C300" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D300" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E300" s="12" t="inlineStr">
-        <is>
-          <t>554-35.265</t>
-        </is>
-      </c>
+          <t>Клапан фреоновый саленоидный</t>
+        </is>
+      </c>
+      <c r="C300" s="5" t="inlineStr"/>
+      <c r="D300" s="5" t="inlineStr"/>
+      <c r="E300" s="7" t="inlineStr"/>
       <c r="F300" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G300" s="9" t="n">
-        <v>0.6</v>
+        <v>12.3</v>
       </c>
       <c r="H300" s="10" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="I300" s="11" t="n"/>
       <c r="J300" s="11" t="n"/>
     </row>
-    <row r="301" ht="22" customHeight="1">
-      <c r="A301" s="4" t="inlineStr">
-        <is>
-          <t>Редукционные клапаны — 3 позиции  11 шт  258 кг</t>
-        </is>
-      </c>
-      <c r="B301" s="4" t="n"/>
-      <c r="C301" s="4" t="n"/>
-      <c r="D301" s="4" t="n"/>
-      <c r="E301" s="4" t="n"/>
-      <c r="F301" s="4" t="n"/>
-      <c r="G301" s="4" t="n"/>
-      <c r="H301" s="4" t="n"/>
-      <c r="I301" s="4" t="n"/>
-      <c r="J301" s="4" t="n"/>
-    </row>
-    <row r="302" ht="26" customHeight="1">
-      <c r="A302" s="5" t="n">
-        <v>278</v>
-      </c>
-      <c r="B302" s="6" t="inlineStr">
-        <is>
-          <t>Клапан редукционный штуц.проход.односедельный Ду20Ру400 у входа</t>
-        </is>
-      </c>
-      <c r="C302" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D302" s="5" t="n">
-        <v>400</v>
-      </c>
-      <c r="E302" s="12" t="inlineStr">
-        <is>
-          <t>525-03.044</t>
-        </is>
-      </c>
-      <c r="F302" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="G302" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="H302" s="10" t="n">
-        <v>243</v>
-      </c>
-      <c r="I302" s="11" t="n"/>
-      <c r="J302" s="11" t="n"/>
+    <row r="301" ht="26" customHeight="1">
+      <c r="A301" s="5" t="n">
+        <v>277</v>
+      </c>
+      <c r="B301" s="6" t="inlineStr">
+        <is>
+          <t>Клапан электромагнитный б/у</t>
+        </is>
+      </c>
+      <c r="C301" s="5" t="inlineStr"/>
+      <c r="D301" s="5" t="inlineStr"/>
+      <c r="E301" s="7" t="inlineStr"/>
+      <c r="F301" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G301" s="9" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H301" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="I301" s="11" t="n"/>
+      <c r="J301" s="11" t="n"/>
+    </row>
+    <row r="302" ht="22" customHeight="1">
+      <c r="A302" s="4" t="inlineStr">
+        <is>
+          <t>Колонка смотровая — 1 позиция  6 шт  9 кг</t>
+        </is>
+      </c>
+      <c r="B302" s="4" t="n"/>
+      <c r="C302" s="4" t="n"/>
+      <c r="D302" s="4" t="n"/>
+      <c r="E302" s="4" t="n"/>
+      <c r="F302" s="4" t="n"/>
+      <c r="G302" s="4" t="n"/>
+      <c r="H302" s="4" t="n"/>
+      <c r="I302" s="4" t="n"/>
+      <c r="J302" s="4" t="n"/>
     </row>
     <row r="303" ht="26" customHeight="1">
       <c r="A303" s="5" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B303" s="6" t="inlineStr">
         <is>
-          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
+          <t>Клапан для колонки указательной Ду10 Ру16</t>
         </is>
       </c>
       <c r="C303" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D303" s="5" t="n">
-        <v>200</v>
+        <v>16</v>
       </c>
       <c r="E303" s="12" t="inlineStr">
         <is>
-          <t>525-35.2634</t>
+          <t>598-03.022-06</t>
         </is>
       </c>
       <c r="F303" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G303" s="9" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="H303" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I303" s="11" t="n"/>
       <c r="J303" s="11" t="n"/>
     </row>
-    <row r="304" ht="26" customHeight="1">
-      <c r="A304" s="5" t="n">
-        <v>280</v>
-      </c>
-      <c r="B304" s="6" t="inlineStr">
-        <is>
-          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
-        </is>
-      </c>
-      <c r="C304" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D304" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E304" s="12" t="inlineStr">
-        <is>
-          <t>525-35.2634-04</t>
-        </is>
-      </c>
-      <c r="F304" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G304" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H304" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="I304" s="11" t="n"/>
-      <c r="J304" s="11" t="n"/>
-    </row>
-    <row r="305" ht="22" customHeight="1">
-      <c r="A305" s="4" t="inlineStr">
-        <is>
-          <t>Электромагнитные клапаны — 4 позиции  7 шт  85 кг</t>
-        </is>
-      </c>
-      <c r="B305" s="4" t="n"/>
-      <c r="C305" s="4" t="n"/>
-      <c r="D305" s="4" t="n"/>
-      <c r="E305" s="4" t="n"/>
-      <c r="F305" s="4" t="n"/>
-      <c r="G305" s="4" t="n"/>
-      <c r="H305" s="4" t="n"/>
-      <c r="I305" s="4" t="n"/>
-      <c r="J305" s="4" t="n"/>
-    </row>
-    <row r="306" ht="26" customHeight="1">
-      <c r="A306" s="5" t="n">
-        <v>281</v>
-      </c>
-      <c r="B306" s="6" t="inlineStr">
-        <is>
-          <t>Клапан с электромагнитным ручным управлением Ду20/10 перем. 220В</t>
-        </is>
-      </c>
-      <c r="C306" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D306" s="5" t="inlineStr"/>
-      <c r="E306" s="12" t="inlineStr">
-        <is>
-          <t>587-35.8490-04</t>
-        </is>
-      </c>
-      <c r="F306" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G306" s="9" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="H306" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="I306" s="11" t="n"/>
-      <c r="J306" s="11" t="n"/>
+    <row r="304" ht="22" customHeight="1">
+      <c r="A304" s="4" t="inlineStr">
+        <is>
+          <t>Эжекторы — 1 позиция  1 шт  4 кг</t>
+        </is>
+      </c>
+      <c r="B304" s="4" t="n"/>
+      <c r="C304" s="4" t="n"/>
+      <c r="D304" s="4" t="n"/>
+      <c r="E304" s="4" t="n"/>
+      <c r="F304" s="4" t="n"/>
+      <c r="G304" s="4" t="n"/>
+      <c r="H304" s="4" t="n"/>
+      <c r="I304" s="4" t="n"/>
+      <c r="J304" s="4" t="n"/>
+    </row>
+    <row r="305" ht="26" customHeight="1">
+      <c r="A305" s="5" t="n">
+        <v>279</v>
+      </c>
+      <c r="B305" s="6" t="inlineStr">
+        <is>
+          <t>Эжектор ВЭЖ 6,3</t>
+        </is>
+      </c>
+      <c r="C305" s="5" t="inlineStr"/>
+      <c r="D305" s="5" t="inlineStr"/>
+      <c r="E305" s="7" t="inlineStr"/>
+      <c r="F305" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G305" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H305" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I305" s="11" t="n"/>
+      <c r="J305" s="11" t="n"/>
+    </row>
+    <row r="306" ht="22" customHeight="1">
+      <c r="A306" s="4" t="inlineStr">
+        <is>
+          <t>Головки вентиляционные — 7 позиций  43 шт  363 кг</t>
+        </is>
+      </c>
+      <c r="B306" s="4" t="n"/>
+      <c r="C306" s="4" t="n"/>
+      <c r="D306" s="4" t="n"/>
+      <c r="E306" s="4" t="n"/>
+      <c r="F306" s="4" t="n"/>
+      <c r="G306" s="4" t="n"/>
+      <c r="H306" s="4" t="n"/>
+      <c r="I306" s="4" t="n"/>
+      <c r="J306" s="4" t="n"/>
     </row>
     <row r="307" ht="26" customHeight="1">
       <c r="A307" s="5" t="n">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B307" s="6" t="inlineStr">
         <is>
-          <t>Клапан с электромагнитным ручным управлением</t>
-        </is>
-      </c>
-      <c r="C307" s="5" t="inlineStr"/>
+          <t>Грибки АМГ Ду 200 с нижнем приводом</t>
+        </is>
+      </c>
+      <c r="C307" s="5" t="n">
+        <v>200</v>
+      </c>
       <c r="D307" s="5" t="inlineStr"/>
       <c r="E307" s="12" t="inlineStr">
         <is>
-          <t>587-182.126</t>
+          <t>(541-03.316-04)</t>
         </is>
       </c>
       <c r="F307" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G307" s="9" t="n">
-        <v>12.3</v>
+        <v>4.7</v>
       </c>
       <c r="H307" s="10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I307" s="11" t="n"/>
       <c r="J307" s="11" t="n"/>
     </row>
     <row r="308" ht="26" customHeight="1">
       <c r="A308" s="5" t="n">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B308" s="6" t="inlineStr">
         <is>
-          <t>Клапан фреоновый саленоидный</t>
-        </is>
-      </c>
-      <c r="C308" s="5" t="inlineStr"/>
+          <t>Грибки АМГ Ду 150 (верхние)</t>
+        </is>
+      </c>
+      <c r="C308" s="5" t="n">
+        <v>150</v>
+      </c>
       <c r="D308" s="5" t="inlineStr"/>
-      <c r="E308" s="7" t="inlineStr"/>
+      <c r="E308" s="12" t="inlineStr">
+        <is>
+          <t>(541-03.315-02)</t>
+        </is>
+      </c>
       <c r="F308" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G308" s="9" t="n">
-        <v>12.3</v>
+        <v>2.9</v>
       </c>
       <c r="H308" s="10" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="I308" s="11" t="n"/>
       <c r="J308" s="11" t="n"/>
     </row>
     <row r="309" ht="26" customHeight="1">
       <c r="A309" s="5" t="n">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B309" s="6" t="inlineStr">
         <is>
-          <t>Клапан электромагнитный б/у</t>
-        </is>
-      </c>
-      <c r="C309" s="5" t="inlineStr"/>
+          <t>Грибки АМГ Ду 150 (нижние)</t>
+        </is>
+      </c>
+      <c r="C309" s="5" t="n">
+        <v>150</v>
+      </c>
       <c r="D309" s="5" t="inlineStr"/>
-      <c r="E309" s="7" t="inlineStr"/>
+      <c r="E309" s="12" t="inlineStr">
+        <is>
+          <t>(541-03.316-02)</t>
+        </is>
+      </c>
       <c r="F309" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G309" s="9" t="n">
-        <v>12.3</v>
+        <v>2.7</v>
       </c>
       <c r="H309" s="10" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="I309" s="11" t="n"/>
       <c r="J309" s="11" t="n"/>
     </row>
-    <row r="310" ht="22" customHeight="1">
-      <c r="A310" s="4" t="inlineStr">
-        <is>
-          <t>Колонка смотровая — 1 позиция  6 шт  9 кг</t>
-        </is>
-      </c>
-      <c r="B310" s="4" t="n"/>
-      <c r="C310" s="4" t="n"/>
-      <c r="D310" s="4" t="n"/>
-      <c r="E310" s="4" t="n"/>
-      <c r="F310" s="4" t="n"/>
-      <c r="G310" s="4" t="n"/>
-      <c r="H310" s="4" t="n"/>
-      <c r="I310" s="4" t="n"/>
-      <c r="J310" s="4" t="n"/>
+    <row r="310" ht="26" customHeight="1">
+      <c r="A310" s="5" t="n">
+        <v>283</v>
+      </c>
+      <c r="B310" s="6" t="inlineStr">
+        <is>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду125 (без поплавка)</t>
+        </is>
+      </c>
+      <c r="C310" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D310" s="5" t="inlineStr"/>
+      <c r="E310" s="12" t="inlineStr">
+        <is>
+          <t>(541-03.220)</t>
+        </is>
+      </c>
+      <c r="F310" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G310" s="9" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H310" s="10" t="n">
+        <v>109</v>
+      </c>
+      <c r="I310" s="11" t="n"/>
+      <c r="J310" s="11" t="n"/>
     </row>
     <row r="311" ht="26" customHeight="1">
       <c r="A311" s="5" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B311" s="6" t="inlineStr">
         <is>
-          <t>Клапан для колонки указательной Ду10 Ру16</t>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду80</t>
         </is>
       </c>
       <c r="C311" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D311" s="5" t="n">
-        <v>16</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D311" s="5" t="inlineStr"/>
       <c r="E311" s="12" t="inlineStr">
         <is>
-          <t>598-03.022-06</t>
+          <t>(541-03.218)</t>
         </is>
       </c>
       <c r="F311" s="8" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G311" s="9" t="n">
-        <v>1.5</v>
+        <v>11.2</v>
       </c>
       <c r="H311" s="10" t="n">
-        <v>9</v>
+        <v>213</v>
       </c>
       <c r="I311" s="11" t="n"/>
       <c r="J311" s="11" t="n"/>
     </row>
-    <row r="312" ht="22" customHeight="1">
-      <c r="A312" s="4" t="inlineStr">
-        <is>
-          <t>Эжекторы — 1 позиция  1 шт  4 кг</t>
-        </is>
-      </c>
-      <c r="B312" s="4" t="n"/>
-      <c r="C312" s="4" t="n"/>
-      <c r="D312" s="4" t="n"/>
-      <c r="E312" s="4" t="n"/>
-      <c r="F312" s="4" t="n"/>
-      <c r="G312" s="4" t="n"/>
-      <c r="H312" s="4" t="n"/>
-      <c r="I312" s="4" t="n"/>
-      <c r="J312" s="4" t="n"/>
+    <row r="312" ht="26" customHeight="1">
+      <c r="A312" s="5" t="n">
+        <v>285</v>
+      </c>
+      <c r="B312" s="6" t="inlineStr">
+        <is>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду32</t>
+        </is>
+      </c>
+      <c r="C312" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="D312" s="5" t="inlineStr"/>
+      <c r="E312" s="12" t="inlineStr">
+        <is>
+          <t>541-03.224</t>
+        </is>
+      </c>
+      <c r="F312" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G312" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H312" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I312" s="11" t="n"/>
+      <c r="J312" s="11" t="n"/>
     </row>
     <row r="313" ht="26" customHeight="1">
       <c r="A313" s="5" t="n">
@@ -9778,20 +9772,26 @@
       </c>
       <c r="B313" s="6" t="inlineStr">
         <is>
-          <t>Эжектор ВЭЖ 6,3</t>
-        </is>
-      </c>
-      <c r="C313" s="5" t="inlineStr"/>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду25</t>
+        </is>
+      </c>
+      <c r="C313" s="5" t="n">
+        <v>25</v>
+      </c>
       <c r="D313" s="5" t="inlineStr"/>
-      <c r="E313" s="7" t="inlineStr"/>
+      <c r="E313" s="12" t="inlineStr">
+        <is>
+          <t>(541-03.232)</t>
+        </is>
+      </c>
       <c r="F313" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G313" s="9" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="H313" s="10" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I313" s="11" t="n"/>
       <c r="J313" s="11" t="n"/>
@@ -9825,7 +9825,7 @@
     <row r="317" ht="30" customHeight="1">
       <c r="A317" s="17" t="inlineStr">
         <is>
-          <t>— Идти сверху вниз: сначала клинкеты и крупное, потом мелочь. В этом же порядке потом грузим контейнер.</t>
+          <t>— Идти сверху вниз: сначала клинкеты и крупное, потом мелочь, в конце вентиляционные головки. В этом же порядке потом грузим контейнер.</t>
         </is>
       </c>
     </row>

--- a/outputs/marine_equipment/Перечень_для_отгрузки.xlsx
+++ b/outputs/marine_equipment/Перечень_для_отгрузки.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Перечень для отгрузки" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Перечень для отгрузки" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень для отгрузки'!$A$5:$J$313</definedName>
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>286 позиций  2 902 шт  27.30 т. Порядок как грузим: сверху самая крупная арматура  дальше по убыванию диаметра  в самом конце вентиляционные головки.</t>
+          <t>286 позиций  2 902 шт  28.99 т. Порядок как грузим: сверху самая крупная арматура  дальше по убыванию диаметра  в самом конце вентиляционные головки.</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Клинкеты — 24 позиции  225 шт  10 703 кг</t>
+          <t>Клинкеты — 24 позиции  225 шт  12 294 кг</t>
         </is>
       </c>
       <c r="B6" s="4" t="n"/>
@@ -830,10 +830,10 @@
         <v>11</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>495</v>
+        <v>352</v>
       </c>
       <c r="I14" s="11" t="n"/>
       <c r="J14" s="11" t="n"/>
@@ -856,10 +856,10 @@
         <v>2</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>19.2</v>
+        <v>32</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="11" t="n"/>
@@ -882,10 +882,10 @@
         <v>6</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>19.2</v>
+        <v>32</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>115</v>
+        <v>192</v>
       </c>
       <c r="I16" s="11" t="n"/>
       <c r="J16" s="11" t="n"/>
@@ -908,10 +908,10 @@
         <v>43</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>19.2</v>
+        <v>32</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>824</v>
+        <v>1376</v>
       </c>
       <c r="I17" s="11" t="n"/>
       <c r="J17" s="11" t="n"/>
@@ -934,10 +934,10 @@
         <v>1</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="I18" s="11" t="n"/>
       <c r="J18" s="11" t="n"/>
@@ -960,10 +960,10 @@
         <v>2</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>19.2</v>
+        <v>32</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="I19" s="11" t="n"/>
       <c r="J19" s="11" t="n"/>
@@ -986,10 +986,10 @@
         <v>1</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>11.7</v>
+        <v>24</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I20" s="11" t="n"/>
       <c r="J20" s="11" t="n"/>
@@ -1012,10 +1012,10 @@
         <v>44</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>11.7</v>
+        <v>24</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>516</v>
+        <v>1056</v>
       </c>
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="11" t="n"/>
@@ -1038,10 +1038,10 @@
         <v>2</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>11.7</v>
+        <v>24</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="I22" s="11" t="n"/>
       <c r="J22" s="11" t="n"/>
@@ -1068,10 +1068,10 @@
         <v>18</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>11.7</v>
+        <v>24</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>211</v>
+        <v>432</v>
       </c>
       <c r="I23" s="11" t="n"/>
       <c r="J23" s="11" t="n"/>
@@ -1098,10 +1098,10 @@
         <v>7</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>8.699999999999999</v>
+        <v>20</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="I24" s="11" t="n"/>
       <c r="J24" s="11" t="n"/>
@@ -1124,10 +1124,10 @@
         <v>16</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>7.4</v>
+        <v>17.9</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>119</v>
+        <v>286</v>
       </c>
       <c r="I25" s="11" t="n"/>
       <c r="J25" s="11" t="n"/>
@@ -1150,10 +1150,10 @@
         <v>1</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>6.2</v>
+        <v>14</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I26" s="11" t="n"/>
       <c r="J26" s="11" t="n"/>
@@ -1176,10 +1176,10 @@
         <v>1</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>6.2</v>
+        <v>14</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I27" s="11" t="n"/>
       <c r="J27" s="11" t="n"/>
@@ -1202,10 +1202,10 @@
         <v>1</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I28" s="11" t="n"/>
       <c r="J28" s="11" t="n"/>
@@ -1265,7 +1265,7 @@
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Фланцевая проходная — 34 позиции  300 шт  4 199 кг</t>
+          <t>Фланцевая проходная — 34 позиции  300 шт  4 257 кг</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1348,10 +1348,10 @@
         <v>2</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>68.7</v>
+        <v>75</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="I34" s="11" t="n"/>
       <c r="J34" s="11" t="n"/>
@@ -1578,10 +1578,10 @@
         <v>5</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="I41" s="11" t="n"/>
       <c r="J41" s="11" t="n"/>
@@ -1612,10 +1612,10 @@
         <v>2</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I42" s="11" t="n"/>
       <c r="J42" s="11" t="n"/>
@@ -2094,10 +2094,10 @@
         <v>13</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="I58" s="11" t="n"/>
       <c r="J58" s="11" t="n"/>
@@ -2120,10 +2120,10 @@
         <v>6</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="I59" s="11" t="n"/>
       <c r="J59" s="11" t="n"/>
@@ -2154,10 +2154,10 @@
         <v>2</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I60" s="11" t="n"/>
       <c r="J60" s="11" t="n"/>
@@ -2188,10 +2188,10 @@
         <v>6</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="I61" s="11" t="n"/>
       <c r="J61" s="11" t="n"/>
@@ -2222,10 +2222,10 @@
         <v>1</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I62" s="11" t="n"/>
       <c r="J62" s="11" t="n"/>
@@ -2286,10 +2286,10 @@
         <v>8</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="I64" s="11" t="n"/>
       <c r="J64" s="11" t="n"/>
@@ -2321,7 +2321,7 @@
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Фильтры забортной воды — 9 позиций  28 шт  1 828 кг</t>
+          <t>Фильтры забортной воды — 9 позиций  28 шт  1 834 кг</t>
         </is>
       </c>
       <c r="B66" s="4" t="n"/>
@@ -2542,10 +2542,10 @@
         <v>1</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I74" s="11" t="n"/>
       <c r="J74" s="11" t="n"/>
@@ -2579,7 +2579,7 @@
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Фланцевая угловая — 27 позиций  100 шт  1 748 кг</t>
+          <t>Фланцевая угловая — 27 позиций  100 шт  1 788 кг</t>
         </is>
       </c>
       <c r="B76" s="4" t="n"/>
@@ -2614,10 +2614,10 @@
         <v>1</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>68.7</v>
+        <v>75</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I77" s="11" t="n"/>
       <c r="J77" s="11" t="n"/>
@@ -2648,10 +2648,10 @@
         <v>1</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>68.7</v>
+        <v>75</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I78" s="11" t="n"/>
       <c r="J78" s="11" t="n"/>
@@ -3118,10 +3118,10 @@
         <v>3</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="I93" s="11" t="n"/>
       <c r="J93" s="11" t="n"/>
@@ -3152,10 +3152,10 @@
         <v>1</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I94" s="11" t="n"/>
       <c r="J94" s="11" t="n"/>
@@ -3186,10 +3186,10 @@
         <v>1</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="H95" s="10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I95" s="11" t="n"/>
       <c r="J95" s="11" t="n"/>
@@ -3220,10 +3220,10 @@
         <v>2</v>
       </c>
       <c r="G96" s="9" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="H96" s="10" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I96" s="11" t="n"/>
       <c r="J96" s="11" t="n"/>
@@ -3250,10 +3250,10 @@
         <v>1</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="H97" s="10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I97" s="11" t="n"/>
       <c r="J97" s="11" t="n"/>
